--- a/ACME_Project_Team_Workload.xlsx
+++ b/ACME_Project_Team_Workload.xlsx
@@ -16,7 +16,9 @@
     <sheet name="RACI" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Risks_Issues" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Resource_Workload" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Dashboard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Summary_ART" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Summary_Team" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Dashboard" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -537,6 +539,1697 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ART</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total Cap/Sprint</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>S1 Hrs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>S2 Hrs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>S3 Hrs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>S4 Hrs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>S5 Hrs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>S6 Hrs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>S7 Hrs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>S8 Hrs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Total Hrs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Util %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Util %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Over/Under Hrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ART 1</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(Resource_Workload!$D:$D,$A2)</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$P:$P)</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$Q:$Q)</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$T:$T)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$V:$V)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$W:$W)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$X:$X)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>IFERROR(L2/(C2*8),0)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$Y:$Y)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$Z:$Z)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ART 2</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTIF(Resource_Workload!$D:$D,$A3)</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$P:$P)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$Q:$Q)</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$T:$T)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$V:$V)</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$W:$W)</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$X:$X)</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>IFERROR(L3/(C3*8),0)</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$Y:$Y)</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$Z:$Z)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ART 3</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(Resource_Workload!$D:$D,$A4)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$P:$P)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$Q:$Q)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$T:$T)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$V:$V)</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$W:$W)</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$X:$X)</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>IFERROR(L4/(C4*8),0)</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$Y:$Y)</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$Z:$Z)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ART 4</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>COUNTIF(Resource_Workload!$D:$D,$A5)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$P:$P)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$Q:$Q)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$T:$T)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$V:$V)</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$W:$W)</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$X:$X)</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>IFERROR(L5/(C5*8),0)</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$Y:$Y)</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$Z:$Z)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ART 5</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(Resource_Workload!$D:$D,$A6)</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$P:$P)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$Q:$Q)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$T:$T)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$V:$V)</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$W:$W)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$X:$X)</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>IFERROR(L6/(C6*8),0)</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$Y:$Y)</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$Z:$Z)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ART 6</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>COUNTIF(Resource_Workload!$D:$D,$A7)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$P:$P)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$Q:$Q)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$T:$T)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$V:$V)</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$W:$W)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$X:$X)</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>IFERROR(L7/(C7*8),0)</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$Y:$Y)</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$Z:$Z)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ART 7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(Resource_Workload!$D:$D,$A8)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$P:$P)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$Q:$Q)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$T:$T)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$V:$V)</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$W:$W)</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$X:$X)</f>
+        <v/>
+      </c>
+      <c r="M8">
+        <f>IFERROR(L8/(C8*8),0)</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$Y:$Y)</f>
+        <v/>
+      </c>
+      <c r="O8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$Z:$Z)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ART</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total Cap/Sprint</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>S1 Hrs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>S2 Hrs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>S3 Hrs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>S4 Hrs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>S5 Hrs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>S6 Hrs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>S7 Hrs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>S8 Hrs</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Total Hrs</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Util %</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Util %</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Over/Under Hrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ART 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Team Alpha</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Justice League Command</t>
+        </is>
+      </c>
+      <c r="D2">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>IFERROR(N2/(E2*8),0)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="Q2">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ART 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Team Beta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Avengers Interface</t>
+        </is>
+      </c>
+      <c r="D3">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>IFERROR(N3/(E3*8),0)</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ART 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Team Alpha</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>X-Men Flight</t>
+        </is>
+      </c>
+      <c r="D4">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>IFERROR(N4/(E4*8),0)</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ART 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Team Beta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fantastic Four Navigation</t>
+        </is>
+      </c>
+      <c r="D5">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>IFERROR(N5/(E5*8),0)</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ART 3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Team Alpha</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Teen Titans Communication</t>
+        </is>
+      </c>
+      <c r="D6">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>IFERROR(N6/(E6*8),0)</f>
+        <v/>
+      </c>
+      <c r="P6">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="Q6">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ART 3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Team Beta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Guardians of the Network</t>
+        </is>
+      </c>
+      <c r="D7">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>IFERROR(N7/(E7*8),0)</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="Q7">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ART 4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Team Alpha</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S.H.I.E.L.D. Security</t>
+        </is>
+      </c>
+      <c r="D8">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="M8">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="O8">
+        <f>IFERROR(N8/(E8*8),0)</f>
+        <v/>
+      </c>
+      <c r="P8">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="Q8">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ART 4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Team Beta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Watchmen Intrusion</t>
+        </is>
+      </c>
+      <c r="D9">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="O9">
+        <f>IFERROR(N9/(E9*8),0)</f>
+        <v/>
+      </c>
+      <c r="P9">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="Q9">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ART 5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Team Alpha</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avengers Intelligence</t>
+        </is>
+      </c>
+      <c r="D10">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="M10">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="O10">
+        <f>IFERROR(N10/(E10*8),0)</f>
+        <v/>
+      </c>
+      <c r="P10">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="Q10">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ART 5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Team Beta</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Justice League Analytics</t>
+        </is>
+      </c>
+      <c r="D11">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="M11">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="O11">
+        <f>IFERROR(N11/(E11*8),0)</f>
+        <v/>
+      </c>
+      <c r="P11">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="Q11">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ART 6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Team Alpha</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>X-Men Coordination</t>
+        </is>
+      </c>
+      <c r="D12">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="M12">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="O12">
+        <f>IFERROR(N12/(E12*8),0)</f>
+        <v/>
+      </c>
+      <c r="P12">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="Q12">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ART 6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Team Beta</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fantastic Four Intelligence</t>
+        </is>
+      </c>
+      <c r="D13">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="O13">
+        <f>IFERROR(N13/(E13*8),0)</f>
+        <v/>
+      </c>
+      <c r="P13">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="Q13">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ART 7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Team Alpha</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avengers Assembly</t>
+        </is>
+      </c>
+      <c r="D14">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="M14">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="O14">
+        <f>IFERROR(N14/(E14*8),0)</f>
+        <v/>
+      </c>
+      <c r="P14">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="Q14">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ART 7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Team Beta</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Justice League Validation</t>
+        </is>
+      </c>
+      <c r="D15">
+        <f>COUNTIFS(Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUMIFS(Resource_Workload!$G:$G,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="J15">
+        <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="M15">
+        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="O15">
+        <f>IFERROR(N15/(E15*8),0)</f>
+        <v/>
+      </c>
+      <c r="P15">
+        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="Q15">
+        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/ACME_Project_Team_Workload.xlsx
+++ b/ACME_Project_Team_Workload.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -607,30 +607,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>S7 Hrs</t>
+          <t>Total Hrs</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>S8 Hrs</t>
+          <t>Overall Util %</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Total Hrs</t>
+          <t>Avg Util %</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Overall Util %</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Util %</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Over/Under Hrs</t>
         </is>
@@ -651,51 +641,43 @@
         <v/>
       </c>
       <c r="D2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="F2">
         <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$P:$P)</f>
         <v/>
       </c>
-      <c r="E2">
+      <c r="G2">
         <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$Q:$Q)</f>
         <v/>
       </c>
-      <c r="F2">
+      <c r="H2">
         <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$R:$R)</f>
         <v/>
       </c>
-      <c r="G2">
+      <c r="I2">
         <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$S:$S)</f>
         <v/>
       </c>
-      <c r="H2">
+      <c r="J2">
         <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$T:$T)</f>
         <v/>
       </c>
-      <c r="I2">
-        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$U:$U)</f>
-        <v/>
-      </c>
-      <c r="J2">
+      <c r="K2">
+        <f>IFERROR(J2/(C2*6),0)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="M2">
         <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$V:$V)</f>
-        <v/>
-      </c>
-      <c r="K2">
-        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$W:$W)</f>
-        <v/>
-      </c>
-      <c r="L2">
-        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$X:$X)</f>
-        <v/>
-      </c>
-      <c r="M2">
-        <f>IFERROR(L2/(C2*8),0)</f>
-        <v/>
-      </c>
-      <c r="N2">
-        <f>AVERAGEIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$Y:$Y)</f>
-        <v/>
-      </c>
-      <c r="O2">
-        <f>SUMIF(Resource_Workload!$D:$D,$A2,Resource_Workload!$Z:$Z)</f>
         <v/>
       </c>
     </row>
@@ -714,51 +696,43 @@
         <v/>
       </c>
       <c r="D3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="F3">
         <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$P:$P)</f>
         <v/>
       </c>
-      <c r="E3">
+      <c r="G3">
         <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$Q:$Q)</f>
         <v/>
       </c>
-      <c r="F3">
+      <c r="H3">
         <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$R:$R)</f>
         <v/>
       </c>
-      <c r="G3">
+      <c r="I3">
         <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$S:$S)</f>
         <v/>
       </c>
-      <c r="H3">
+      <c r="J3">
         <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$T:$T)</f>
         <v/>
       </c>
-      <c r="I3">
-        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$U:$U)</f>
-        <v/>
-      </c>
-      <c r="J3">
+      <c r="K3">
+        <f>IFERROR(J3/(C3*6),0)</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="M3">
         <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$V:$V)</f>
-        <v/>
-      </c>
-      <c r="K3">
-        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$W:$W)</f>
-        <v/>
-      </c>
-      <c r="L3">
-        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$X:$X)</f>
-        <v/>
-      </c>
-      <c r="M3">
-        <f>IFERROR(L3/(C3*8),0)</f>
-        <v/>
-      </c>
-      <c r="N3">
-        <f>AVERAGEIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$Y:$Y)</f>
-        <v/>
-      </c>
-      <c r="O3">
-        <f>SUMIF(Resource_Workload!$D:$D,$A3,Resource_Workload!$Z:$Z)</f>
         <v/>
       </c>
     </row>
@@ -777,51 +751,43 @@
         <v/>
       </c>
       <c r="D4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="F4">
         <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$P:$P)</f>
         <v/>
       </c>
-      <c r="E4">
+      <c r="G4">
         <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$Q:$Q)</f>
         <v/>
       </c>
-      <c r="F4">
+      <c r="H4">
         <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$R:$R)</f>
         <v/>
       </c>
-      <c r="G4">
+      <c r="I4">
         <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$S:$S)</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="J4">
         <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$T:$T)</f>
         <v/>
       </c>
-      <c r="I4">
-        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$U:$U)</f>
-        <v/>
-      </c>
-      <c r="J4">
+      <c r="K4">
+        <f>IFERROR(J4/(C4*6),0)</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="M4">
         <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$V:$V)</f>
-        <v/>
-      </c>
-      <c r="K4">
-        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$W:$W)</f>
-        <v/>
-      </c>
-      <c r="L4">
-        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$X:$X)</f>
-        <v/>
-      </c>
-      <c r="M4">
-        <f>IFERROR(L4/(C4*8),0)</f>
-        <v/>
-      </c>
-      <c r="N4">
-        <f>AVERAGEIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$Y:$Y)</f>
-        <v/>
-      </c>
-      <c r="O4">
-        <f>SUMIF(Resource_Workload!$D:$D,$A4,Resource_Workload!$Z:$Z)</f>
         <v/>
       </c>
     </row>
@@ -840,51 +806,43 @@
         <v/>
       </c>
       <c r="D5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="F5">
         <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$P:$P)</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="G5">
         <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$Q:$Q)</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="H5">
         <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$R:$R)</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="I5">
         <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$S:$S)</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="J5">
         <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$T:$T)</f>
         <v/>
       </c>
-      <c r="I5">
-        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$U:$U)</f>
-        <v/>
-      </c>
-      <c r="J5">
+      <c r="K5">
+        <f>IFERROR(J5/(C5*6),0)</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="M5">
         <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$V:$V)</f>
-        <v/>
-      </c>
-      <c r="K5">
-        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$W:$W)</f>
-        <v/>
-      </c>
-      <c r="L5">
-        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$X:$X)</f>
-        <v/>
-      </c>
-      <c r="M5">
-        <f>IFERROR(L5/(C5*8),0)</f>
-        <v/>
-      </c>
-      <c r="N5">
-        <f>AVERAGEIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$Y:$Y)</f>
-        <v/>
-      </c>
-      <c r="O5">
-        <f>SUMIF(Resource_Workload!$D:$D,$A5,Resource_Workload!$Z:$Z)</f>
         <v/>
       </c>
     </row>
@@ -903,51 +861,43 @@
         <v/>
       </c>
       <c r="D6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="F6">
         <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$P:$P)</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="G6">
         <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$Q:$Q)</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="H6">
         <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$R:$R)</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="I6">
         <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$S:$S)</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="J6">
         <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$T:$T)</f>
         <v/>
       </c>
-      <c r="I6">
-        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$U:$U)</f>
-        <v/>
-      </c>
-      <c r="J6">
+      <c r="K6">
+        <f>IFERROR(J6/(C6*6),0)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="M6">
         <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$V:$V)</f>
-        <v/>
-      </c>
-      <c r="K6">
-        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$W:$W)</f>
-        <v/>
-      </c>
-      <c r="L6">
-        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$X:$X)</f>
-        <v/>
-      </c>
-      <c r="M6">
-        <f>IFERROR(L6/(C6*8),0)</f>
-        <v/>
-      </c>
-      <c r="N6">
-        <f>AVERAGEIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$Y:$Y)</f>
-        <v/>
-      </c>
-      <c r="O6">
-        <f>SUMIF(Resource_Workload!$D:$D,$A6,Resource_Workload!$Z:$Z)</f>
         <v/>
       </c>
     </row>
@@ -966,51 +916,43 @@
         <v/>
       </c>
       <c r="D7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="F7">
         <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$P:$P)</f>
         <v/>
       </c>
-      <c r="E7">
+      <c r="G7">
         <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$Q:$Q)</f>
         <v/>
       </c>
-      <c r="F7">
+      <c r="H7">
         <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$R:$R)</f>
         <v/>
       </c>
-      <c r="G7">
+      <c r="I7">
         <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$S:$S)</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="J7">
         <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$T:$T)</f>
         <v/>
       </c>
-      <c r="I7">
-        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$U:$U)</f>
-        <v/>
-      </c>
-      <c r="J7">
+      <c r="K7">
+        <f>IFERROR(J7/(C7*6),0)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="M7">
         <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$V:$V)</f>
-        <v/>
-      </c>
-      <c r="K7">
-        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$W:$W)</f>
-        <v/>
-      </c>
-      <c r="L7">
-        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$X:$X)</f>
-        <v/>
-      </c>
-      <c r="M7">
-        <f>IFERROR(L7/(C7*8),0)</f>
-        <v/>
-      </c>
-      <c r="N7">
-        <f>AVERAGEIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$Y:$Y)</f>
-        <v/>
-      </c>
-      <c r="O7">
-        <f>SUMIF(Resource_Workload!$D:$D,$A7,Resource_Workload!$Z:$Z)</f>
         <v/>
       </c>
     </row>
@@ -1029,51 +971,43 @@
         <v/>
       </c>
       <c r="D8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="F8">
         <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$P:$P)</f>
         <v/>
       </c>
-      <c r="E8">
+      <c r="G8">
         <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$Q:$Q)</f>
         <v/>
       </c>
-      <c r="F8">
+      <c r="H8">
         <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$R:$R)</f>
         <v/>
       </c>
-      <c r="G8">
+      <c r="I8">
         <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$S:$S)</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="J8">
         <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$T:$T)</f>
         <v/>
       </c>
-      <c r="I8">
-        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$U:$U)</f>
-        <v/>
-      </c>
-      <c r="J8">
+      <c r="K8">
+        <f>IFERROR(J8/(C8*6),0)</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>AVERAGEIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$U:$U)</f>
+        <v/>
+      </c>
+      <c r="M8">
         <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$V:$V)</f>
-        <v/>
-      </c>
-      <c r="K8">
-        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$W:$W)</f>
-        <v/>
-      </c>
-      <c r="L8">
-        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$X:$X)</f>
-        <v/>
-      </c>
-      <c r="M8">
-        <f>IFERROR(L8/(C8*8),0)</f>
-        <v/>
-      </c>
-      <c r="N8">
-        <f>AVERAGEIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$Y:$Y)</f>
-        <v/>
-      </c>
-      <c r="O8">
-        <f>SUMIF(Resource_Workload!$D:$D,$A8,Resource_Workload!$Z:$Z)</f>
         <v/>
       </c>
     </row>
@@ -1088,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1168,30 +1102,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>S7 Hrs</t>
+          <t>Total Hrs</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>S8 Hrs</t>
+          <t>Overall Util %</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Total Hrs</t>
+          <t>Avg Util %</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Overall Util %</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Util %</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Over/Under Hrs</t>
         </is>
@@ -1222,51 +1146,43 @@
         <v/>
       </c>
       <c r="F2">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="H2">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
         <v/>
       </c>
-      <c r="G2">
+      <c r="I2">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
         <v/>
       </c>
-      <c r="H2">
+      <c r="J2">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
         <v/>
       </c>
-      <c r="I2">
+      <c r="K2">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
         <v/>
       </c>
-      <c r="J2">
+      <c r="L2">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
         <v/>
       </c>
-      <c r="K2">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
-        <v/>
-      </c>
-      <c r="L2">
+      <c r="M2">
+        <f>IFERROR(L2/(E2*6),0)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
+        <v/>
+      </c>
+      <c r="O2">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
-        <v/>
-      </c>
-      <c r="M2">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
-        <v/>
-      </c>
-      <c r="N2">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
-        <v/>
-      </c>
-      <c r="O2">
-        <f>IFERROR(N2/(E2*8),0)</f>
-        <v/>
-      </c>
-      <c r="P2">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
-        <v/>
-      </c>
-      <c r="Q2">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A2,Resource_Workload!$E:$E,$B2,Resource_Workload!$F:$F,$C2)</f>
         <v/>
       </c>
     </row>
@@ -1295,51 +1211,43 @@
         <v/>
       </c>
       <c r="F3">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="H3">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
         <v/>
       </c>
-      <c r="G3">
+      <c r="I3">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
         <v/>
       </c>
-      <c r="H3">
+      <c r="J3">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
         <v/>
       </c>
-      <c r="I3">
+      <c r="K3">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
         <v/>
       </c>
-      <c r="J3">
+      <c r="L3">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
         <v/>
       </c>
-      <c r="K3">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
-        <v/>
-      </c>
-      <c r="L3">
+      <c r="M3">
+        <f>IFERROR(L3/(E3*6),0)</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
+        <v/>
+      </c>
+      <c r="O3">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
-        <v/>
-      </c>
-      <c r="M3">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
-        <v/>
-      </c>
-      <c r="N3">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
-        <v/>
-      </c>
-      <c r="O3">
-        <f>IFERROR(N3/(E3*8),0)</f>
-        <v/>
-      </c>
-      <c r="P3">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
-        <v/>
-      </c>
-      <c r="Q3">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A3,Resource_Workload!$E:$E,$B3,Resource_Workload!$F:$F,$C3)</f>
         <v/>
       </c>
     </row>
@@ -1368,51 +1276,43 @@
         <v/>
       </c>
       <c r="F4">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="H4">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
         <v/>
       </c>
-      <c r="G4">
+      <c r="I4">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="J4">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
         <v/>
       </c>
-      <c r="I4">
+      <c r="K4">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
         <v/>
       </c>
-      <c r="J4">
+      <c r="L4">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
         <v/>
       </c>
-      <c r="K4">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
-        <v/>
-      </c>
-      <c r="L4">
+      <c r="M4">
+        <f>IFERROR(L4/(E4*6),0)</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
+        <v/>
+      </c>
+      <c r="O4">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
-        <v/>
-      </c>
-      <c r="M4">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
-        <v/>
-      </c>
-      <c r="N4">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
-        <v/>
-      </c>
-      <c r="O4">
-        <f>IFERROR(N4/(E4*8),0)</f>
-        <v/>
-      </c>
-      <c r="P4">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
-        <v/>
-      </c>
-      <c r="Q4">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A4,Resource_Workload!$E:$E,$B4,Resource_Workload!$F:$F,$C4)</f>
         <v/>
       </c>
     </row>
@@ -1441,51 +1341,43 @@
         <v/>
       </c>
       <c r="F5">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="H5">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="I5">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="J5">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
         <v/>
       </c>
-      <c r="I5">
+      <c r="K5">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
         <v/>
       </c>
-      <c r="J5">
+      <c r="L5">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
         <v/>
       </c>
-      <c r="K5">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
-        <v/>
-      </c>
-      <c r="L5">
+      <c r="M5">
+        <f>IFERROR(L5/(E5*6),0)</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
+        <v/>
+      </c>
+      <c r="O5">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
-        <v/>
-      </c>
-      <c r="M5">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
-        <v/>
-      </c>
-      <c r="N5">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
-        <v/>
-      </c>
-      <c r="O5">
-        <f>IFERROR(N5/(E5*8),0)</f>
-        <v/>
-      </c>
-      <c r="P5">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
-        <v/>
-      </c>
-      <c r="Q5">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A5,Resource_Workload!$E:$E,$B5,Resource_Workload!$F:$F,$C5)</f>
         <v/>
       </c>
     </row>
@@ -1514,51 +1406,43 @@
         <v/>
       </c>
       <c r="F6">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="H6">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="I6">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="J6">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
         <v/>
       </c>
-      <c r="I6">
+      <c r="K6">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
         <v/>
       </c>
-      <c r="J6">
+      <c r="L6">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
         <v/>
       </c>
-      <c r="K6">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
-        <v/>
-      </c>
-      <c r="L6">
+      <c r="M6">
+        <f>IFERROR(L6/(E6*6),0)</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
+        <v/>
+      </c>
+      <c r="O6">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
-        <v/>
-      </c>
-      <c r="M6">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
-        <v/>
-      </c>
-      <c r="N6">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
-        <v/>
-      </c>
-      <c r="O6">
-        <f>IFERROR(N6/(E6*8),0)</f>
-        <v/>
-      </c>
-      <c r="P6">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
-        <v/>
-      </c>
-      <c r="Q6">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A6,Resource_Workload!$E:$E,$B6,Resource_Workload!$F:$F,$C6)</f>
         <v/>
       </c>
     </row>
@@ -1587,51 +1471,43 @@
         <v/>
       </c>
       <c r="F7">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="H7">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
         <v/>
       </c>
-      <c r="G7">
+      <c r="I7">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="J7">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
         <v/>
       </c>
-      <c r="I7">
+      <c r="K7">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
         <v/>
       </c>
-      <c r="J7">
+      <c r="L7">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
         <v/>
       </c>
-      <c r="K7">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
-        <v/>
-      </c>
-      <c r="L7">
+      <c r="M7">
+        <f>IFERROR(L7/(E7*6),0)</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
+        <v/>
+      </c>
+      <c r="O7">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
-        <v/>
-      </c>
-      <c r="M7">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
-        <v/>
-      </c>
-      <c r="N7">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
-        <v/>
-      </c>
-      <c r="O7">
-        <f>IFERROR(N7/(E7*8),0)</f>
-        <v/>
-      </c>
-      <c r="P7">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
-        <v/>
-      </c>
-      <c r="Q7">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A7,Resource_Workload!$E:$E,$B7,Resource_Workload!$F:$F,$C7)</f>
         <v/>
       </c>
     </row>
@@ -1660,51 +1536,43 @@
         <v/>
       </c>
       <c r="F8">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="H8">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
         <v/>
       </c>
-      <c r="G8">
+      <c r="I8">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="J8">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
         <v/>
       </c>
-      <c r="I8">
+      <c r="K8">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
         <v/>
       </c>
-      <c r="J8">
+      <c r="L8">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
         <v/>
       </c>
-      <c r="K8">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
-        <v/>
-      </c>
-      <c r="L8">
+      <c r="M8">
+        <f>IFERROR(L8/(E8*6),0)</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
+        <v/>
+      </c>
+      <c r="O8">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
-        <v/>
-      </c>
-      <c r="M8">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
-        <v/>
-      </c>
-      <c r="N8">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
-        <v/>
-      </c>
-      <c r="O8">
-        <f>IFERROR(N8/(E8*8),0)</f>
-        <v/>
-      </c>
-      <c r="P8">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
-        <v/>
-      </c>
-      <c r="Q8">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A8,Resource_Workload!$E:$E,$B8,Resource_Workload!$F:$F,$C8)</f>
         <v/>
       </c>
     </row>
@@ -1733,51 +1601,43 @@
         <v/>
       </c>
       <c r="F9">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="H9">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
         <v/>
       </c>
-      <c r="G9">
+      <c r="I9">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
         <v/>
       </c>
-      <c r="H9">
+      <c r="J9">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
         <v/>
       </c>
-      <c r="I9">
+      <c r="K9">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
         <v/>
       </c>
-      <c r="J9">
+      <c r="L9">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
         <v/>
       </c>
-      <c r="K9">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
-        <v/>
-      </c>
-      <c r="L9">
+      <c r="M9">
+        <f>IFERROR(L9/(E9*6),0)</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
+        <v/>
+      </c>
+      <c r="O9">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
-        <v/>
-      </c>
-      <c r="M9">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
-        <v/>
-      </c>
-      <c r="N9">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
-        <v/>
-      </c>
-      <c r="O9">
-        <f>IFERROR(N9/(E9*8),0)</f>
-        <v/>
-      </c>
-      <c r="P9">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
-        <v/>
-      </c>
-      <c r="Q9">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A9,Resource_Workload!$E:$E,$B9,Resource_Workload!$F:$F,$C9)</f>
         <v/>
       </c>
     </row>
@@ -1806,51 +1666,43 @@
         <v/>
       </c>
       <c r="F10">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="H10">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
         <v/>
       </c>
-      <c r="G10">
+      <c r="I10">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
         <v/>
       </c>
-      <c r="H10">
+      <c r="J10">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
         <v/>
       </c>
-      <c r="I10">
+      <c r="K10">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
         <v/>
       </c>
-      <c r="J10">
+      <c r="L10">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
         <v/>
       </c>
-      <c r="K10">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
-        <v/>
-      </c>
-      <c r="L10">
+      <c r="M10">
+        <f>IFERROR(L10/(E10*6),0)</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
+        <v/>
+      </c>
+      <c r="O10">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
-        <v/>
-      </c>
-      <c r="M10">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
-        <v/>
-      </c>
-      <c r="N10">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
-        <v/>
-      </c>
-      <c r="O10">
-        <f>IFERROR(N10/(E10*8),0)</f>
-        <v/>
-      </c>
-      <c r="P10">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
-        <v/>
-      </c>
-      <c r="Q10">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A10,Resource_Workload!$E:$E,$B10,Resource_Workload!$F:$F,$C10)</f>
         <v/>
       </c>
     </row>
@@ -1879,51 +1731,43 @@
         <v/>
       </c>
       <c r="F11">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="H11">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
         <v/>
       </c>
-      <c r="G11">
+      <c r="I11">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
         <v/>
       </c>
-      <c r="H11">
+      <c r="J11">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
         <v/>
       </c>
-      <c r="I11">
+      <c r="K11">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
         <v/>
       </c>
-      <c r="J11">
+      <c r="L11">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
         <v/>
       </c>
-      <c r="K11">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
-        <v/>
-      </c>
-      <c r="L11">
+      <c r="M11">
+        <f>IFERROR(L11/(E11*6),0)</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
+        <v/>
+      </c>
+      <c r="O11">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
-        <v/>
-      </c>
-      <c r="M11">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
-        <v/>
-      </c>
-      <c r="N11">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
-        <v/>
-      </c>
-      <c r="O11">
-        <f>IFERROR(N11/(E11*8),0)</f>
-        <v/>
-      </c>
-      <c r="P11">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
-        <v/>
-      </c>
-      <c r="Q11">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A11,Resource_Workload!$E:$E,$B11,Resource_Workload!$F:$F,$C11)</f>
         <v/>
       </c>
     </row>
@@ -1952,51 +1796,43 @@
         <v/>
       </c>
       <c r="F12">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="H12">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
         <v/>
       </c>
-      <c r="G12">
+      <c r="I12">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
         <v/>
       </c>
-      <c r="H12">
+      <c r="J12">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
         <v/>
       </c>
-      <c r="I12">
+      <c r="K12">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
         <v/>
       </c>
-      <c r="J12">
+      <c r="L12">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
         <v/>
       </c>
-      <c r="K12">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
-        <v/>
-      </c>
-      <c r="L12">
+      <c r="M12">
+        <f>IFERROR(L12/(E12*6),0)</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
+        <v/>
+      </c>
+      <c r="O12">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
-        <v/>
-      </c>
-      <c r="M12">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
-        <v/>
-      </c>
-      <c r="N12">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
-        <v/>
-      </c>
-      <c r="O12">
-        <f>IFERROR(N12/(E12*8),0)</f>
-        <v/>
-      </c>
-      <c r="P12">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
-        <v/>
-      </c>
-      <c r="Q12">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A12,Resource_Workload!$E:$E,$B12,Resource_Workload!$F:$F,$C12)</f>
         <v/>
       </c>
     </row>
@@ -2025,51 +1861,43 @@
         <v/>
       </c>
       <c r="F13">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="H13">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
         <v/>
       </c>
-      <c r="G13">
+      <c r="I13">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
         <v/>
       </c>
-      <c r="H13">
+      <c r="J13">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
         <v/>
       </c>
-      <c r="I13">
+      <c r="K13">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
         <v/>
       </c>
-      <c r="J13">
+      <c r="L13">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
         <v/>
       </c>
-      <c r="K13">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
-        <v/>
-      </c>
-      <c r="L13">
+      <c r="M13">
+        <f>IFERROR(L13/(E13*6),0)</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
+        <v/>
+      </c>
+      <c r="O13">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
-        <v/>
-      </c>
-      <c r="M13">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
-        <v/>
-      </c>
-      <c r="N13">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
-        <v/>
-      </c>
-      <c r="O13">
-        <f>IFERROR(N13/(E13*8),0)</f>
-        <v/>
-      </c>
-      <c r="P13">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
-        <v/>
-      </c>
-      <c r="Q13">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A13,Resource_Workload!$E:$E,$B13,Resource_Workload!$F:$F,$C13)</f>
         <v/>
       </c>
     </row>
@@ -2098,51 +1926,43 @@
         <v/>
       </c>
       <c r="F14">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="H14">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
         <v/>
       </c>
-      <c r="G14">
+      <c r="I14">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
         <v/>
       </c>
-      <c r="H14">
+      <c r="J14">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
         <v/>
       </c>
-      <c r="I14">
+      <c r="K14">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
         <v/>
       </c>
-      <c r="J14">
+      <c r="L14">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
         <v/>
       </c>
-      <c r="K14">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
-        <v/>
-      </c>
-      <c r="L14">
+      <c r="M14">
+        <f>IFERROR(L14/(E14*6),0)</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
+        <v/>
+      </c>
+      <c r="O14">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
-        <v/>
-      </c>
-      <c r="M14">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
-        <v/>
-      </c>
-      <c r="N14">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
-        <v/>
-      </c>
-      <c r="O14">
-        <f>IFERROR(N14/(E14*8),0)</f>
-        <v/>
-      </c>
-      <c r="P14">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
-        <v/>
-      </c>
-      <c r="Q14">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A14,Resource_Workload!$E:$E,$B14,Resource_Workload!$F:$F,$C14)</f>
         <v/>
       </c>
     </row>
@@ -2171,51 +1991,43 @@
         <v/>
       </c>
       <c r="F15">
+        <f>SUMIFS(Resource_Workload!$N:$N,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>SUMIFS(Resource_Workload!$O:$O,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="H15">
         <f>SUMIFS(Resource_Workload!$P:$P,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
         <v/>
       </c>
-      <c r="G15">
+      <c r="I15">
         <f>SUMIFS(Resource_Workload!$Q:$Q,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
         <v/>
       </c>
-      <c r="H15">
+      <c r="J15">
         <f>SUMIFS(Resource_Workload!$R:$R,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
         <v/>
       </c>
-      <c r="I15">
+      <c r="K15">
         <f>SUMIFS(Resource_Workload!$S:$S,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
         <v/>
       </c>
-      <c r="J15">
+      <c r="L15">
         <f>SUMIFS(Resource_Workload!$T:$T,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
         <v/>
       </c>
-      <c r="K15">
-        <f>SUMIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
-        <v/>
-      </c>
-      <c r="L15">
+      <c r="M15">
+        <f>IFERROR(L15/(E15*6),0)</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>AVERAGEIFS(Resource_Workload!$U:$U,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
+        <v/>
+      </c>
+      <c r="O15">
         <f>SUMIFS(Resource_Workload!$V:$V,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
-        <v/>
-      </c>
-      <c r="M15">
-        <f>SUMIFS(Resource_Workload!$W:$W,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
-        <v/>
-      </c>
-      <c r="N15">
-        <f>SUMIFS(Resource_Workload!$X:$X,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
-        <v/>
-      </c>
-      <c r="O15">
-        <f>IFERROR(N15/(E15*8),0)</f>
-        <v/>
-      </c>
-      <c r="P15">
-        <f>AVERAGEIFS(Resource_Workload!$Y:$Y,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
-        <v/>
-      </c>
-      <c r="Q15">
-        <f>SUMIFS(Resource_Workload!$Z:$Z,Resource_Workload!$D:$D,$A15,Resource_Workload!$E:$E,$B15,Resource_Workload!$F:$F,$C15)</f>
         <v/>
       </c>
     </row>
@@ -2267,7 +2079,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>AVERAGE(Resource_Workload!Y:Y)</f>
+        <f>AVERAGE(Resource_Workload!U:U)</f>
         <v/>
       </c>
     </row>
@@ -2278,7 +2090,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Resource_Workload!Y:Y,"&gt;1")</f>
+        <f>COUNTIF(Resource_Workload!U:U,"&gt;1")</f>
         <v/>
       </c>
     </row>
@@ -2293,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2337,11 +2149,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2352,16 +2164,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2372,16 +2184,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2392,16 +2204,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2412,16 +2224,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2432,56 +2244,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sprint 8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -9893,7 +9665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z92"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9909,19 +9681,15 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9992,65 +9760,45 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>S7 %</t>
+          <t>S1 Hrs</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>S8 %</t>
+          <t>S2 Hrs</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>S1 Hrs</t>
+          <t>S3 Hrs</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>S2 Hrs</t>
+          <t>S4 Hrs</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>S3 Hrs</t>
+          <t>S5 Hrs</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>S4 Hrs</t>
+          <t>S6 Hrs</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>S5 Hrs</t>
+          <t>Total Hrs</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>S6 Hrs</t>
+          <t>Avg Util %</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>S7 Hrs</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S8 Hrs</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Total Hrs</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Util %</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Over/Under Hrs</t>
         </is>
@@ -10088,7 +9836,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -10108,54 +9856,40 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
+      <c r="N2">
+        <f>G2*H2</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>G2*I2</f>
+        <v/>
       </c>
       <c r="P2">
-        <f>G2*H2</f>
+        <f>G2*J2</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>G2*I2</f>
+        <f>G2*K2</f>
         <v/>
       </c>
       <c r="R2">
-        <f>G2*J2</f>
+        <f>G2*L2</f>
         <v/>
       </c>
       <c r="S2">
-        <f>G2*K2</f>
+        <f>G2*M2</f>
         <v/>
       </c>
       <c r="T2">
-        <f>G2*L2</f>
+        <f>SUM(N2:S2)</f>
         <v/>
       </c>
       <c r="U2">
-        <f>G2*M2</f>
+        <f>AVERAGE(H2:M2)</f>
         <v/>
       </c>
       <c r="V2">
-        <f>G2*N2</f>
-        <v/>
-      </c>
-      <c r="W2">
-        <f>G2*O2</f>
-        <v/>
-      </c>
-      <c r="X2">
-        <f>SUM(P2:W2)</f>
-        <v/>
-      </c>
-      <c r="Y2">
-        <f>AVERAGE(H2:O2)</f>
-        <v/>
-      </c>
-      <c r="Z2">
-        <f>X2-G2*8</f>
+        <f>T2-G2*6</f>
         <v/>
       </c>
     </row>
@@ -10191,7 +9925,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -10211,54 +9945,40 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
+      <c r="N3">
+        <f>G3*H3</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>G3*I3</f>
+        <v/>
       </c>
       <c r="P3">
-        <f>G3*H3</f>
+        <f>G3*J3</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>G3*I3</f>
+        <f>G3*K3</f>
         <v/>
       </c>
       <c r="R3">
-        <f>G3*J3</f>
+        <f>G3*L3</f>
         <v/>
       </c>
       <c r="S3">
-        <f>G3*K3</f>
+        <f>G3*M3</f>
         <v/>
       </c>
       <c r="T3">
-        <f>G3*L3</f>
+        <f>SUM(N3:S3)</f>
         <v/>
       </c>
       <c r="U3">
-        <f>G3*M3</f>
+        <f>AVERAGE(H3:M3)</f>
         <v/>
       </c>
       <c r="V3">
-        <f>G3*N3</f>
-        <v/>
-      </c>
-      <c r="W3">
-        <f>G3*O3</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>SUM(P3:W3)</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>AVERAGE(H3:O3)</f>
-        <v/>
-      </c>
-      <c r="Z3">
-        <f>X3-G3*8</f>
+        <f>T3-G3*6</f>
         <v/>
       </c>
     </row>
@@ -10294,7 +10014,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -10314,54 +10034,40 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
+      <c r="N4">
+        <f>G4*H4</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>G4*I4</f>
+        <v/>
       </c>
       <c r="P4">
-        <f>G4*H4</f>
+        <f>G4*J4</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>G4*I4</f>
+        <f>G4*K4</f>
         <v/>
       </c>
       <c r="R4">
-        <f>G4*J4</f>
+        <f>G4*L4</f>
         <v/>
       </c>
       <c r="S4">
-        <f>G4*K4</f>
+        <f>G4*M4</f>
         <v/>
       </c>
       <c r="T4">
-        <f>G4*L4</f>
+        <f>SUM(N4:S4)</f>
         <v/>
       </c>
       <c r="U4">
-        <f>G4*M4</f>
+        <f>AVERAGE(H4:M4)</f>
         <v/>
       </c>
       <c r="V4">
-        <f>G4*N4</f>
-        <v/>
-      </c>
-      <c r="W4">
-        <f>G4*O4</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>SUM(P4:W4)</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(H4:O4)</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>X4-G4*8</f>
+        <f>T4-G4*6</f>
         <v/>
       </c>
     </row>
@@ -10397,7 +10103,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -10417,54 +10123,40 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
+      <c r="N5">
+        <f>G5*H5</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>G5*I5</f>
+        <v/>
       </c>
       <c r="P5">
-        <f>G5*H5</f>
+        <f>G5*J5</f>
         <v/>
       </c>
       <c r="Q5">
-        <f>G5*I5</f>
+        <f>G5*K5</f>
         <v/>
       </c>
       <c r="R5">
-        <f>G5*J5</f>
+        <f>G5*L5</f>
         <v/>
       </c>
       <c r="S5">
-        <f>G5*K5</f>
+        <f>G5*M5</f>
         <v/>
       </c>
       <c r="T5">
-        <f>G5*L5</f>
+        <f>SUM(N5:S5)</f>
         <v/>
       </c>
       <c r="U5">
-        <f>G5*M5</f>
+        <f>AVERAGE(H5:M5)</f>
         <v/>
       </c>
       <c r="V5">
-        <f>G5*N5</f>
-        <v/>
-      </c>
-      <c r="W5">
-        <f>G5*O5</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>SUM(P5:W5)</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>AVERAGE(H5:O5)</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>X5-G5*8</f>
+        <f>T5-G5*6</f>
         <v/>
       </c>
     </row>
@@ -10500,7 +10192,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -10520,54 +10212,40 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
+      <c r="N6">
+        <f>G6*H6</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>G6*I6</f>
+        <v/>
       </c>
       <c r="P6">
-        <f>G6*H6</f>
+        <f>G6*J6</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>G6*I6</f>
+        <f>G6*K6</f>
         <v/>
       </c>
       <c r="R6">
-        <f>G6*J6</f>
+        <f>G6*L6</f>
         <v/>
       </c>
       <c r="S6">
-        <f>G6*K6</f>
+        <f>G6*M6</f>
         <v/>
       </c>
       <c r="T6">
-        <f>G6*L6</f>
+        <f>SUM(N6:S6)</f>
         <v/>
       </c>
       <c r="U6">
-        <f>G6*M6</f>
+        <f>AVERAGE(H6:M6)</f>
         <v/>
       </c>
       <c r="V6">
-        <f>G6*N6</f>
-        <v/>
-      </c>
-      <c r="W6">
-        <f>G6*O6</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>SUM(P6:W6)</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>AVERAGE(H6:O6)</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>X6-G6*8</f>
+        <f>T6-G6*6</f>
         <v/>
       </c>
     </row>
@@ -10603,7 +10281,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -10623,54 +10301,40 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
+      <c r="N7">
+        <f>G7*H7</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>G7*I7</f>
+        <v/>
       </c>
       <c r="P7">
-        <f>G7*H7</f>
+        <f>G7*J7</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>G7*I7</f>
+        <f>G7*K7</f>
         <v/>
       </c>
       <c r="R7">
-        <f>G7*J7</f>
+        <f>G7*L7</f>
         <v/>
       </c>
       <c r="S7">
-        <f>G7*K7</f>
+        <f>G7*M7</f>
         <v/>
       </c>
       <c r="T7">
-        <f>G7*L7</f>
+        <f>SUM(N7:S7)</f>
         <v/>
       </c>
       <c r="U7">
-        <f>G7*M7</f>
+        <f>AVERAGE(H7:M7)</f>
         <v/>
       </c>
       <c r="V7">
-        <f>G7*N7</f>
-        <v/>
-      </c>
-      <c r="W7">
-        <f>G7*O7</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>SUM(P7:W7)</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>AVERAGE(H7:O7)</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>X7-G7*8</f>
+        <f>T7-G7*6</f>
         <v/>
       </c>
     </row>
@@ -10706,7 +10370,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10726,54 +10390,40 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
+      <c r="N8">
+        <f>G8*H8</f>
+        <v/>
+      </c>
+      <c r="O8">
+        <f>G8*I8</f>
+        <v/>
       </c>
       <c r="P8">
-        <f>G8*H8</f>
+        <f>G8*J8</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>G8*I8</f>
+        <f>G8*K8</f>
         <v/>
       </c>
       <c r="R8">
-        <f>G8*J8</f>
+        <f>G8*L8</f>
         <v/>
       </c>
       <c r="S8">
-        <f>G8*K8</f>
+        <f>G8*M8</f>
         <v/>
       </c>
       <c r="T8">
-        <f>G8*L8</f>
+        <f>SUM(N8:S8)</f>
         <v/>
       </c>
       <c r="U8">
-        <f>G8*M8</f>
+        <f>AVERAGE(H8:M8)</f>
         <v/>
       </c>
       <c r="V8">
-        <f>G8*N8</f>
-        <v/>
-      </c>
-      <c r="W8">
-        <f>G8*O8</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>SUM(P8:W8)</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>AVERAGE(H8:O8)</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>X8-G8*8</f>
+        <f>T8-G8*6</f>
         <v/>
       </c>
     </row>
@@ -10809,7 +10459,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10829,54 +10479,40 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
+      <c r="N9">
+        <f>G9*H9</f>
+        <v/>
+      </c>
+      <c r="O9">
+        <f>G9*I9</f>
+        <v/>
       </c>
       <c r="P9">
-        <f>G9*H9</f>
+        <f>G9*J9</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>G9*I9</f>
+        <f>G9*K9</f>
         <v/>
       </c>
       <c r="R9">
-        <f>G9*J9</f>
+        <f>G9*L9</f>
         <v/>
       </c>
       <c r="S9">
-        <f>G9*K9</f>
+        <f>G9*M9</f>
         <v/>
       </c>
       <c r="T9">
-        <f>G9*L9</f>
+        <f>SUM(N9:S9)</f>
         <v/>
       </c>
       <c r="U9">
-        <f>G9*M9</f>
+        <f>AVERAGE(H9:M9)</f>
         <v/>
       </c>
       <c r="V9">
-        <f>G9*N9</f>
-        <v/>
-      </c>
-      <c r="W9">
-        <f>G9*O9</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>SUM(P9:W9)</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>AVERAGE(H9:O9)</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>X9-G9*8</f>
+        <f>T9-G9*6</f>
         <v/>
       </c>
     </row>
@@ -10912,7 +10548,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10932,54 +10568,40 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
+      <c r="N10">
+        <f>G10*H10</f>
+        <v/>
+      </c>
+      <c r="O10">
+        <f>G10*I10</f>
+        <v/>
       </c>
       <c r="P10">
-        <f>G10*H10</f>
+        <f>G10*J10</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>G10*I10</f>
+        <f>G10*K10</f>
         <v/>
       </c>
       <c r="R10">
-        <f>G10*J10</f>
+        <f>G10*L10</f>
         <v/>
       </c>
       <c r="S10">
-        <f>G10*K10</f>
+        <f>G10*M10</f>
         <v/>
       </c>
       <c r="T10">
-        <f>G10*L10</f>
+        <f>SUM(N10:S10)</f>
         <v/>
       </c>
       <c r="U10">
-        <f>G10*M10</f>
+        <f>AVERAGE(H10:M10)</f>
         <v/>
       </c>
       <c r="V10">
-        <f>G10*N10</f>
-        <v/>
-      </c>
-      <c r="W10">
-        <f>G10*O10</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>SUM(P10:W10)</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>AVERAGE(H10:O10)</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>X10-G10*8</f>
+        <f>T10-G10*6</f>
         <v/>
       </c>
     </row>
@@ -11015,7 +10637,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -11035,54 +10657,40 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
+      <c r="N11">
+        <f>G11*H11</f>
+        <v/>
+      </c>
+      <c r="O11">
+        <f>G11*I11</f>
+        <v/>
       </c>
       <c r="P11">
-        <f>G11*H11</f>
+        <f>G11*J11</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>G11*I11</f>
+        <f>G11*K11</f>
         <v/>
       </c>
       <c r="R11">
-        <f>G11*J11</f>
+        <f>G11*L11</f>
         <v/>
       </c>
       <c r="S11">
-        <f>G11*K11</f>
+        <f>G11*M11</f>
         <v/>
       </c>
       <c r="T11">
-        <f>G11*L11</f>
+        <f>SUM(N11:S11)</f>
         <v/>
       </c>
       <c r="U11">
-        <f>G11*M11</f>
+        <f>AVERAGE(H11:M11)</f>
         <v/>
       </c>
       <c r="V11">
-        <f>G11*N11</f>
-        <v/>
-      </c>
-      <c r="W11">
-        <f>G11*O11</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>SUM(P11:W11)</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>AVERAGE(H11:O11)</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>X11-G11*8</f>
+        <f>T11-G11*6</f>
         <v/>
       </c>
     </row>
@@ -11118,7 +10726,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -11138,54 +10746,40 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
+      <c r="N12">
+        <f>G12*H12</f>
+        <v/>
+      </c>
+      <c r="O12">
+        <f>G12*I12</f>
+        <v/>
       </c>
       <c r="P12">
-        <f>G12*H12</f>
+        <f>G12*J12</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>G12*I12</f>
+        <f>G12*K12</f>
         <v/>
       </c>
       <c r="R12">
-        <f>G12*J12</f>
+        <f>G12*L12</f>
         <v/>
       </c>
       <c r="S12">
-        <f>G12*K12</f>
+        <f>G12*M12</f>
         <v/>
       </c>
       <c r="T12">
-        <f>G12*L12</f>
+        <f>SUM(N12:S12)</f>
         <v/>
       </c>
       <c r="U12">
-        <f>G12*M12</f>
+        <f>AVERAGE(H12:M12)</f>
         <v/>
       </c>
       <c r="V12">
-        <f>G12*N12</f>
-        <v/>
-      </c>
-      <c r="W12">
-        <f>G12*O12</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>SUM(P12:W12)</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>AVERAGE(H12:O12)</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>X12-G12*8</f>
+        <f>T12-G12*6</f>
         <v/>
       </c>
     </row>
@@ -11221,7 +10815,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -11241,54 +10835,40 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
+      <c r="N13">
+        <f>G13*H13</f>
+        <v/>
+      </c>
+      <c r="O13">
+        <f>G13*I13</f>
+        <v/>
       </c>
       <c r="P13">
-        <f>G13*H13</f>
+        <f>G13*J13</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>G13*I13</f>
+        <f>G13*K13</f>
         <v/>
       </c>
       <c r="R13">
-        <f>G13*J13</f>
+        <f>G13*L13</f>
         <v/>
       </c>
       <c r="S13">
-        <f>G13*K13</f>
+        <f>G13*M13</f>
         <v/>
       </c>
       <c r="T13">
-        <f>G13*L13</f>
+        <f>SUM(N13:S13)</f>
         <v/>
       </c>
       <c r="U13">
-        <f>G13*M13</f>
+        <f>AVERAGE(H13:M13)</f>
         <v/>
       </c>
       <c r="V13">
-        <f>G13*N13</f>
-        <v/>
-      </c>
-      <c r="W13">
-        <f>G13*O13</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>SUM(P13:W13)</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>AVERAGE(H13:O13)</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>X13-G13*8</f>
+        <f>T13-G13*6</f>
         <v/>
       </c>
     </row>
@@ -11324,7 +10904,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -11344,54 +10924,40 @@
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
+      <c r="N14">
+        <f>G14*H14</f>
+        <v/>
+      </c>
+      <c r="O14">
+        <f>G14*I14</f>
+        <v/>
       </c>
       <c r="P14">
-        <f>G14*H14</f>
+        <f>G14*J14</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>G14*I14</f>
+        <f>G14*K14</f>
         <v/>
       </c>
       <c r="R14">
-        <f>G14*J14</f>
+        <f>G14*L14</f>
         <v/>
       </c>
       <c r="S14">
-        <f>G14*K14</f>
+        <f>G14*M14</f>
         <v/>
       </c>
       <c r="T14">
-        <f>G14*L14</f>
+        <f>SUM(N14:S14)</f>
         <v/>
       </c>
       <c r="U14">
-        <f>G14*M14</f>
+        <f>AVERAGE(H14:M14)</f>
         <v/>
       </c>
       <c r="V14">
-        <f>G14*N14</f>
-        <v/>
-      </c>
-      <c r="W14">
-        <f>G14*O14</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>SUM(P14:W14)</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>AVERAGE(H14:O14)</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>X14-G14*8</f>
+        <f>T14-G14*6</f>
         <v/>
       </c>
     </row>
@@ -11427,7 +10993,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -11447,54 +11013,40 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
+      <c r="N15">
+        <f>G15*H15</f>
+        <v/>
+      </c>
+      <c r="O15">
+        <f>G15*I15</f>
+        <v/>
       </c>
       <c r="P15">
-        <f>G15*H15</f>
+        <f>G15*J15</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>G15*I15</f>
+        <f>G15*K15</f>
         <v/>
       </c>
       <c r="R15">
-        <f>G15*J15</f>
+        <f>G15*L15</f>
         <v/>
       </c>
       <c r="S15">
-        <f>G15*K15</f>
+        <f>G15*M15</f>
         <v/>
       </c>
       <c r="T15">
-        <f>G15*L15</f>
+        <f>SUM(N15:S15)</f>
         <v/>
       </c>
       <c r="U15">
-        <f>G15*M15</f>
+        <f>AVERAGE(H15:M15)</f>
         <v/>
       </c>
       <c r="V15">
-        <f>G15*N15</f>
-        <v/>
-      </c>
-      <c r="W15">
-        <f>G15*O15</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>SUM(P15:W15)</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>AVERAGE(H15:O15)</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>X15-G15*8</f>
+        <f>T15-G15*6</f>
         <v/>
       </c>
     </row>
@@ -11530,7 +11082,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -11550,54 +11102,40 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
+      <c r="N16">
+        <f>G16*H16</f>
+        <v/>
+      </c>
+      <c r="O16">
+        <f>G16*I16</f>
+        <v/>
       </c>
       <c r="P16">
-        <f>G16*H16</f>
+        <f>G16*J16</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>G16*I16</f>
+        <f>G16*K16</f>
         <v/>
       </c>
       <c r="R16">
-        <f>G16*J16</f>
+        <f>G16*L16</f>
         <v/>
       </c>
       <c r="S16">
-        <f>G16*K16</f>
+        <f>G16*M16</f>
         <v/>
       </c>
       <c r="T16">
-        <f>G16*L16</f>
+        <f>SUM(N16:S16)</f>
         <v/>
       </c>
       <c r="U16">
-        <f>G16*M16</f>
+        <f>AVERAGE(H16:M16)</f>
         <v/>
       </c>
       <c r="V16">
-        <f>G16*N16</f>
-        <v/>
-      </c>
-      <c r="W16">
-        <f>G16*O16</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>SUM(P16:W16)</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>AVERAGE(H16:O16)</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>X16-G16*8</f>
+        <f>T16-G16*6</f>
         <v/>
       </c>
     </row>
@@ -11633,7 +11171,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -11653,54 +11191,40 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
+      <c r="N17">
+        <f>G17*H17</f>
+        <v/>
+      </c>
+      <c r="O17">
+        <f>G17*I17</f>
+        <v/>
       </c>
       <c r="P17">
-        <f>G17*H17</f>
+        <f>G17*J17</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>G17*I17</f>
+        <f>G17*K17</f>
         <v/>
       </c>
       <c r="R17">
-        <f>G17*J17</f>
+        <f>G17*L17</f>
         <v/>
       </c>
       <c r="S17">
-        <f>G17*K17</f>
+        <f>G17*M17</f>
         <v/>
       </c>
       <c r="T17">
-        <f>G17*L17</f>
+        <f>SUM(N17:S17)</f>
         <v/>
       </c>
       <c r="U17">
-        <f>G17*M17</f>
+        <f>AVERAGE(H17:M17)</f>
         <v/>
       </c>
       <c r="V17">
-        <f>G17*N17</f>
-        <v/>
-      </c>
-      <c r="W17">
-        <f>G17*O17</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>SUM(P17:W17)</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>AVERAGE(H17:O17)</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>X17-G17*8</f>
+        <f>T17-G17*6</f>
         <v/>
       </c>
     </row>
@@ -11736,7 +11260,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -11756,54 +11280,40 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
+      <c r="N18">
+        <f>G18*H18</f>
+        <v/>
+      </c>
+      <c r="O18">
+        <f>G18*I18</f>
+        <v/>
       </c>
       <c r="P18">
-        <f>G18*H18</f>
+        <f>G18*J18</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>G18*I18</f>
+        <f>G18*K18</f>
         <v/>
       </c>
       <c r="R18">
-        <f>G18*J18</f>
+        <f>G18*L18</f>
         <v/>
       </c>
       <c r="S18">
-        <f>G18*K18</f>
+        <f>G18*M18</f>
         <v/>
       </c>
       <c r="T18">
-        <f>G18*L18</f>
+        <f>SUM(N18:S18)</f>
         <v/>
       </c>
       <c r="U18">
-        <f>G18*M18</f>
+        <f>AVERAGE(H18:M18)</f>
         <v/>
       </c>
       <c r="V18">
-        <f>G18*N18</f>
-        <v/>
-      </c>
-      <c r="W18">
-        <f>G18*O18</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>SUM(P18:W18)</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>AVERAGE(H18:O18)</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>X18-G18*8</f>
+        <f>T18-G18*6</f>
         <v/>
       </c>
     </row>
@@ -11839,7 +11349,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -11859,54 +11369,40 @@
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
+      <c r="N19">
+        <f>G19*H19</f>
+        <v/>
+      </c>
+      <c r="O19">
+        <f>G19*I19</f>
+        <v/>
       </c>
       <c r="P19">
-        <f>G19*H19</f>
+        <f>G19*J19</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>G19*I19</f>
+        <f>G19*K19</f>
         <v/>
       </c>
       <c r="R19">
-        <f>G19*J19</f>
+        <f>G19*L19</f>
         <v/>
       </c>
       <c r="S19">
-        <f>G19*K19</f>
+        <f>G19*M19</f>
         <v/>
       </c>
       <c r="T19">
-        <f>G19*L19</f>
+        <f>SUM(N19:S19)</f>
         <v/>
       </c>
       <c r="U19">
-        <f>G19*M19</f>
+        <f>AVERAGE(H19:M19)</f>
         <v/>
       </c>
       <c r="V19">
-        <f>G19*N19</f>
-        <v/>
-      </c>
-      <c r="W19">
-        <f>G19*O19</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>SUM(P19:W19)</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>AVERAGE(H19:O19)</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>X19-G19*8</f>
+        <f>T19-G19*6</f>
         <v/>
       </c>
     </row>
@@ -11942,7 +11438,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -11962,54 +11458,40 @@
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
+      <c r="N20">
+        <f>G20*H20</f>
+        <v/>
+      </c>
+      <c r="O20">
+        <f>G20*I20</f>
+        <v/>
       </c>
       <c r="P20">
-        <f>G20*H20</f>
+        <f>G20*J20</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>G20*I20</f>
+        <f>G20*K20</f>
         <v/>
       </c>
       <c r="R20">
-        <f>G20*J20</f>
+        <f>G20*L20</f>
         <v/>
       </c>
       <c r="S20">
-        <f>G20*K20</f>
+        <f>G20*M20</f>
         <v/>
       </c>
       <c r="T20">
-        <f>G20*L20</f>
+        <f>SUM(N20:S20)</f>
         <v/>
       </c>
       <c r="U20">
-        <f>G20*M20</f>
+        <f>AVERAGE(H20:M20)</f>
         <v/>
       </c>
       <c r="V20">
-        <f>G20*N20</f>
-        <v/>
-      </c>
-      <c r="W20">
-        <f>G20*O20</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>SUM(P20:W20)</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>AVERAGE(H20:O20)</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>X20-G20*8</f>
+        <f>T20-G20*6</f>
         <v/>
       </c>
     </row>
@@ -12045,7 +11527,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -12065,54 +11547,40 @@
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
+      <c r="N21">
+        <f>G21*H21</f>
+        <v/>
+      </c>
+      <c r="O21">
+        <f>G21*I21</f>
+        <v/>
       </c>
       <c r="P21">
-        <f>G21*H21</f>
+        <f>G21*J21</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>G21*I21</f>
+        <f>G21*K21</f>
         <v/>
       </c>
       <c r="R21">
-        <f>G21*J21</f>
+        <f>G21*L21</f>
         <v/>
       </c>
       <c r="S21">
-        <f>G21*K21</f>
+        <f>G21*M21</f>
         <v/>
       </c>
       <c r="T21">
-        <f>G21*L21</f>
+        <f>SUM(N21:S21)</f>
         <v/>
       </c>
       <c r="U21">
-        <f>G21*M21</f>
+        <f>AVERAGE(H21:M21)</f>
         <v/>
       </c>
       <c r="V21">
-        <f>G21*N21</f>
-        <v/>
-      </c>
-      <c r="W21">
-        <f>G21*O21</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>SUM(P21:W21)</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>AVERAGE(H21:O21)</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>X21-G21*8</f>
+        <f>T21-G21*6</f>
         <v/>
       </c>
     </row>
@@ -12148,7 +11616,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -12168,54 +11636,40 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
+      <c r="N22">
+        <f>G22*H22</f>
+        <v/>
+      </c>
+      <c r="O22">
+        <f>G22*I22</f>
+        <v/>
       </c>
       <c r="P22">
-        <f>G22*H22</f>
+        <f>G22*J22</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>G22*I22</f>
+        <f>G22*K22</f>
         <v/>
       </c>
       <c r="R22">
-        <f>G22*J22</f>
+        <f>G22*L22</f>
         <v/>
       </c>
       <c r="S22">
-        <f>G22*K22</f>
+        <f>G22*M22</f>
         <v/>
       </c>
       <c r="T22">
-        <f>G22*L22</f>
+        <f>SUM(N22:S22)</f>
         <v/>
       </c>
       <c r="U22">
-        <f>G22*M22</f>
+        <f>AVERAGE(H22:M22)</f>
         <v/>
       </c>
       <c r="V22">
-        <f>G22*N22</f>
-        <v/>
-      </c>
-      <c r="W22">
-        <f>G22*O22</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>SUM(P22:W22)</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>AVERAGE(H22:O22)</f>
-        <v/>
-      </c>
-      <c r="Z22">
-        <f>X22-G22*8</f>
+        <f>T22-G22*6</f>
         <v/>
       </c>
     </row>
@@ -12251,7 +11705,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -12271,54 +11725,40 @@
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
+      <c r="N23">
+        <f>G23*H23</f>
+        <v/>
+      </c>
+      <c r="O23">
+        <f>G23*I23</f>
+        <v/>
       </c>
       <c r="P23">
-        <f>G23*H23</f>
+        <f>G23*J23</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>G23*I23</f>
+        <f>G23*K23</f>
         <v/>
       </c>
       <c r="R23">
-        <f>G23*J23</f>
+        <f>G23*L23</f>
         <v/>
       </c>
       <c r="S23">
-        <f>G23*K23</f>
+        <f>G23*M23</f>
         <v/>
       </c>
       <c r="T23">
-        <f>G23*L23</f>
+        <f>SUM(N23:S23)</f>
         <v/>
       </c>
       <c r="U23">
-        <f>G23*M23</f>
+        <f>AVERAGE(H23:M23)</f>
         <v/>
       </c>
       <c r="V23">
-        <f>G23*N23</f>
-        <v/>
-      </c>
-      <c r="W23">
-        <f>G23*O23</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>SUM(P23:W23)</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>AVERAGE(H23:O23)</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>X23-G23*8</f>
+        <f>T23-G23*6</f>
         <v/>
       </c>
     </row>
@@ -12354,7 +11794,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -12374,54 +11814,40 @@
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
+      <c r="N24">
+        <f>G24*H24</f>
+        <v/>
+      </c>
+      <c r="O24">
+        <f>G24*I24</f>
+        <v/>
       </c>
       <c r="P24">
-        <f>G24*H24</f>
+        <f>G24*J24</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>G24*I24</f>
+        <f>G24*K24</f>
         <v/>
       </c>
       <c r="R24">
-        <f>G24*J24</f>
+        <f>G24*L24</f>
         <v/>
       </c>
       <c r="S24">
-        <f>G24*K24</f>
+        <f>G24*M24</f>
         <v/>
       </c>
       <c r="T24">
-        <f>G24*L24</f>
+        <f>SUM(N24:S24)</f>
         <v/>
       </c>
       <c r="U24">
-        <f>G24*M24</f>
+        <f>AVERAGE(H24:M24)</f>
         <v/>
       </c>
       <c r="V24">
-        <f>G24*N24</f>
-        <v/>
-      </c>
-      <c r="W24">
-        <f>G24*O24</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>SUM(P24:W24)</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>AVERAGE(H24:O24)</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>X24-G24*8</f>
+        <f>T24-G24*6</f>
         <v/>
       </c>
     </row>
@@ -12457,7 +11883,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -12477,54 +11903,40 @@
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
+      <c r="N25">
+        <f>G25*H25</f>
+        <v/>
+      </c>
+      <c r="O25">
+        <f>G25*I25</f>
+        <v/>
       </c>
       <c r="P25">
-        <f>G25*H25</f>
+        <f>G25*J25</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>G25*I25</f>
+        <f>G25*K25</f>
         <v/>
       </c>
       <c r="R25">
-        <f>G25*J25</f>
+        <f>G25*L25</f>
         <v/>
       </c>
       <c r="S25">
-        <f>G25*K25</f>
+        <f>G25*M25</f>
         <v/>
       </c>
       <c r="T25">
-        <f>G25*L25</f>
+        <f>SUM(N25:S25)</f>
         <v/>
       </c>
       <c r="U25">
-        <f>G25*M25</f>
+        <f>AVERAGE(H25:M25)</f>
         <v/>
       </c>
       <c r="V25">
-        <f>G25*N25</f>
-        <v/>
-      </c>
-      <c r="W25">
-        <f>G25*O25</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>SUM(P25:W25)</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>AVERAGE(H25:O25)</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>X25-G25*8</f>
+        <f>T25-G25*6</f>
         <v/>
       </c>
     </row>
@@ -12560,7 +11972,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -12580,54 +11992,40 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
+      <c r="N26">
+        <f>G26*H26</f>
+        <v/>
+      </c>
+      <c r="O26">
+        <f>G26*I26</f>
+        <v/>
       </c>
       <c r="P26">
-        <f>G26*H26</f>
+        <f>G26*J26</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>G26*I26</f>
+        <f>G26*K26</f>
         <v/>
       </c>
       <c r="R26">
-        <f>G26*J26</f>
+        <f>G26*L26</f>
         <v/>
       </c>
       <c r="S26">
-        <f>G26*K26</f>
+        <f>G26*M26</f>
         <v/>
       </c>
       <c r="T26">
-        <f>G26*L26</f>
+        <f>SUM(N26:S26)</f>
         <v/>
       </c>
       <c r="U26">
-        <f>G26*M26</f>
+        <f>AVERAGE(H26:M26)</f>
         <v/>
       </c>
       <c r="V26">
-        <f>G26*N26</f>
-        <v/>
-      </c>
-      <c r="W26">
-        <f>G26*O26</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>SUM(P26:W26)</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>AVERAGE(H26:O26)</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>X26-G26*8</f>
+        <f>T26-G26*6</f>
         <v/>
       </c>
     </row>
@@ -12663,7 +12061,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -12683,54 +12081,40 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
+      <c r="N27">
+        <f>G27*H27</f>
+        <v/>
+      </c>
+      <c r="O27">
+        <f>G27*I27</f>
+        <v/>
       </c>
       <c r="P27">
-        <f>G27*H27</f>
+        <f>G27*J27</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>G27*I27</f>
+        <f>G27*K27</f>
         <v/>
       </c>
       <c r="R27">
-        <f>G27*J27</f>
+        <f>G27*L27</f>
         <v/>
       </c>
       <c r="S27">
-        <f>G27*K27</f>
+        <f>G27*M27</f>
         <v/>
       </c>
       <c r="T27">
-        <f>G27*L27</f>
+        <f>SUM(N27:S27)</f>
         <v/>
       </c>
       <c r="U27">
-        <f>G27*M27</f>
+        <f>AVERAGE(H27:M27)</f>
         <v/>
       </c>
       <c r="V27">
-        <f>G27*N27</f>
-        <v/>
-      </c>
-      <c r="W27">
-        <f>G27*O27</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>SUM(P27:W27)</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>AVERAGE(H27:O27)</f>
-        <v/>
-      </c>
-      <c r="Z27">
-        <f>X27-G27*8</f>
+        <f>T27-G27*6</f>
         <v/>
       </c>
     </row>
@@ -12766,7 +12150,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -12786,54 +12170,40 @@
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
+      <c r="N28">
+        <f>G28*H28</f>
+        <v/>
+      </c>
+      <c r="O28">
+        <f>G28*I28</f>
+        <v/>
       </c>
       <c r="P28">
-        <f>G28*H28</f>
+        <f>G28*J28</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>G28*I28</f>
+        <f>G28*K28</f>
         <v/>
       </c>
       <c r="R28">
-        <f>G28*J28</f>
+        <f>G28*L28</f>
         <v/>
       </c>
       <c r="S28">
-        <f>G28*K28</f>
+        <f>G28*M28</f>
         <v/>
       </c>
       <c r="T28">
-        <f>G28*L28</f>
+        <f>SUM(N28:S28)</f>
         <v/>
       </c>
       <c r="U28">
-        <f>G28*M28</f>
+        <f>AVERAGE(H28:M28)</f>
         <v/>
       </c>
       <c r="V28">
-        <f>G28*N28</f>
-        <v/>
-      </c>
-      <c r="W28">
-        <f>G28*O28</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>SUM(P28:W28)</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>AVERAGE(H28:O28)</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>X28-G28*8</f>
+        <f>T28-G28*6</f>
         <v/>
       </c>
     </row>
@@ -12869,7 +12239,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -12889,54 +12259,40 @@
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
+      <c r="N29">
+        <f>G29*H29</f>
+        <v/>
+      </c>
+      <c r="O29">
+        <f>G29*I29</f>
+        <v/>
       </c>
       <c r="P29">
-        <f>G29*H29</f>
+        <f>G29*J29</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>G29*I29</f>
+        <f>G29*K29</f>
         <v/>
       </c>
       <c r="R29">
-        <f>G29*J29</f>
+        <f>G29*L29</f>
         <v/>
       </c>
       <c r="S29">
-        <f>G29*K29</f>
+        <f>G29*M29</f>
         <v/>
       </c>
       <c r="T29">
-        <f>G29*L29</f>
+        <f>SUM(N29:S29)</f>
         <v/>
       </c>
       <c r="U29">
-        <f>G29*M29</f>
+        <f>AVERAGE(H29:M29)</f>
         <v/>
       </c>
       <c r="V29">
-        <f>G29*N29</f>
-        <v/>
-      </c>
-      <c r="W29">
-        <f>G29*O29</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>SUM(P29:W29)</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>AVERAGE(H29:O29)</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>X29-G29*8</f>
+        <f>T29-G29*6</f>
         <v/>
       </c>
     </row>
@@ -12972,7 +12328,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -12992,54 +12348,40 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
+      <c r="N30">
+        <f>G30*H30</f>
+        <v/>
+      </c>
+      <c r="O30">
+        <f>G30*I30</f>
+        <v/>
       </c>
       <c r="P30">
-        <f>G30*H30</f>
+        <f>G30*J30</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>G30*I30</f>
+        <f>G30*K30</f>
         <v/>
       </c>
       <c r="R30">
-        <f>G30*J30</f>
+        <f>G30*L30</f>
         <v/>
       </c>
       <c r="S30">
-        <f>G30*K30</f>
+        <f>G30*M30</f>
         <v/>
       </c>
       <c r="T30">
-        <f>G30*L30</f>
+        <f>SUM(N30:S30)</f>
         <v/>
       </c>
       <c r="U30">
-        <f>G30*M30</f>
+        <f>AVERAGE(H30:M30)</f>
         <v/>
       </c>
       <c r="V30">
-        <f>G30*N30</f>
-        <v/>
-      </c>
-      <c r="W30">
-        <f>G30*O30</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>SUM(P30:W30)</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>AVERAGE(H30:O30)</f>
-        <v/>
-      </c>
-      <c r="Z30">
-        <f>X30-G30*8</f>
+        <f>T30-G30*6</f>
         <v/>
       </c>
     </row>
@@ -13075,7 +12417,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -13095,54 +12437,40 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
+      <c r="N31">
+        <f>G31*H31</f>
+        <v/>
+      </c>
+      <c r="O31">
+        <f>G31*I31</f>
+        <v/>
       </c>
       <c r="P31">
-        <f>G31*H31</f>
+        <f>G31*J31</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>G31*I31</f>
+        <f>G31*K31</f>
         <v/>
       </c>
       <c r="R31">
-        <f>G31*J31</f>
+        <f>G31*L31</f>
         <v/>
       </c>
       <c r="S31">
-        <f>G31*K31</f>
+        <f>G31*M31</f>
         <v/>
       </c>
       <c r="T31">
-        <f>G31*L31</f>
+        <f>SUM(N31:S31)</f>
         <v/>
       </c>
       <c r="U31">
-        <f>G31*M31</f>
+        <f>AVERAGE(H31:M31)</f>
         <v/>
       </c>
       <c r="V31">
-        <f>G31*N31</f>
-        <v/>
-      </c>
-      <c r="W31">
-        <f>G31*O31</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>SUM(P31:W31)</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>AVERAGE(H31:O31)</f>
-        <v/>
-      </c>
-      <c r="Z31">
-        <f>X31-G31*8</f>
+        <f>T31-G31*6</f>
         <v/>
       </c>
     </row>
@@ -13178,7 +12506,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -13198,54 +12526,40 @@
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
+      <c r="N32">
+        <f>G32*H32</f>
+        <v/>
+      </c>
+      <c r="O32">
+        <f>G32*I32</f>
+        <v/>
       </c>
       <c r="P32">
-        <f>G32*H32</f>
+        <f>G32*J32</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>G32*I32</f>
+        <f>G32*K32</f>
         <v/>
       </c>
       <c r="R32">
-        <f>G32*J32</f>
+        <f>G32*L32</f>
         <v/>
       </c>
       <c r="S32">
-        <f>G32*K32</f>
+        <f>G32*M32</f>
         <v/>
       </c>
       <c r="T32">
-        <f>G32*L32</f>
+        <f>SUM(N32:S32)</f>
         <v/>
       </c>
       <c r="U32">
-        <f>G32*M32</f>
+        <f>AVERAGE(H32:M32)</f>
         <v/>
       </c>
       <c r="V32">
-        <f>G32*N32</f>
-        <v/>
-      </c>
-      <c r="W32">
-        <f>G32*O32</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>SUM(P32:W32)</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>AVERAGE(H32:O32)</f>
-        <v/>
-      </c>
-      <c r="Z32">
-        <f>X32-G32*8</f>
+        <f>T32-G32*6</f>
         <v/>
       </c>
     </row>
@@ -13281,7 +12595,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -13301,54 +12615,40 @@
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
+      <c r="N33">
+        <f>G33*H33</f>
+        <v/>
+      </c>
+      <c r="O33">
+        <f>G33*I33</f>
+        <v/>
       </c>
       <c r="P33">
-        <f>G33*H33</f>
+        <f>G33*J33</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>G33*I33</f>
+        <f>G33*K33</f>
         <v/>
       </c>
       <c r="R33">
-        <f>G33*J33</f>
+        <f>G33*L33</f>
         <v/>
       </c>
       <c r="S33">
-        <f>G33*K33</f>
+        <f>G33*M33</f>
         <v/>
       </c>
       <c r="T33">
-        <f>G33*L33</f>
+        <f>SUM(N33:S33)</f>
         <v/>
       </c>
       <c r="U33">
-        <f>G33*M33</f>
+        <f>AVERAGE(H33:M33)</f>
         <v/>
       </c>
       <c r="V33">
-        <f>G33*N33</f>
-        <v/>
-      </c>
-      <c r="W33">
-        <f>G33*O33</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>SUM(P33:W33)</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>AVERAGE(H33:O33)</f>
-        <v/>
-      </c>
-      <c r="Z33">
-        <f>X33-G33*8</f>
+        <f>T33-G33*6</f>
         <v/>
       </c>
     </row>
@@ -13384,7 +12684,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -13404,54 +12704,40 @@
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
+      <c r="N34">
+        <f>G34*H34</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>G34*I34</f>
+        <v/>
       </c>
       <c r="P34">
-        <f>G34*H34</f>
+        <f>G34*J34</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>G34*I34</f>
+        <f>G34*K34</f>
         <v/>
       </c>
       <c r="R34">
-        <f>G34*J34</f>
+        <f>G34*L34</f>
         <v/>
       </c>
       <c r="S34">
-        <f>G34*K34</f>
+        <f>G34*M34</f>
         <v/>
       </c>
       <c r="T34">
-        <f>G34*L34</f>
+        <f>SUM(N34:S34)</f>
         <v/>
       </c>
       <c r="U34">
-        <f>G34*M34</f>
+        <f>AVERAGE(H34:M34)</f>
         <v/>
       </c>
       <c r="V34">
-        <f>G34*N34</f>
-        <v/>
-      </c>
-      <c r="W34">
-        <f>G34*O34</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>SUM(P34:W34)</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>AVERAGE(H34:O34)</f>
-        <v/>
-      </c>
-      <c r="Z34">
-        <f>X34-G34*8</f>
+        <f>T34-G34*6</f>
         <v/>
       </c>
     </row>
@@ -13487,7 +12773,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -13507,54 +12793,40 @@
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
+      <c r="N35">
+        <f>G35*H35</f>
+        <v/>
+      </c>
+      <c r="O35">
+        <f>G35*I35</f>
+        <v/>
       </c>
       <c r="P35">
-        <f>G35*H35</f>
+        <f>G35*J35</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>G35*I35</f>
+        <f>G35*K35</f>
         <v/>
       </c>
       <c r="R35">
-        <f>G35*J35</f>
+        <f>G35*L35</f>
         <v/>
       </c>
       <c r="S35">
-        <f>G35*K35</f>
+        <f>G35*M35</f>
         <v/>
       </c>
       <c r="T35">
-        <f>G35*L35</f>
+        <f>SUM(N35:S35)</f>
         <v/>
       </c>
       <c r="U35">
-        <f>G35*M35</f>
+        <f>AVERAGE(H35:M35)</f>
         <v/>
       </c>
       <c r="V35">
-        <f>G35*N35</f>
-        <v/>
-      </c>
-      <c r="W35">
-        <f>G35*O35</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>SUM(P35:W35)</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>AVERAGE(H35:O35)</f>
-        <v/>
-      </c>
-      <c r="Z35">
-        <f>X35-G35*8</f>
+        <f>T35-G35*6</f>
         <v/>
       </c>
     </row>
@@ -13590,7 +12862,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -13610,54 +12882,40 @@
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
+      <c r="N36">
+        <f>G36*H36</f>
+        <v/>
+      </c>
+      <c r="O36">
+        <f>G36*I36</f>
+        <v/>
       </c>
       <c r="P36">
-        <f>G36*H36</f>
+        <f>G36*J36</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>G36*I36</f>
+        <f>G36*K36</f>
         <v/>
       </c>
       <c r="R36">
-        <f>G36*J36</f>
+        <f>G36*L36</f>
         <v/>
       </c>
       <c r="S36">
-        <f>G36*K36</f>
+        <f>G36*M36</f>
         <v/>
       </c>
       <c r="T36">
-        <f>G36*L36</f>
+        <f>SUM(N36:S36)</f>
         <v/>
       </c>
       <c r="U36">
-        <f>G36*M36</f>
+        <f>AVERAGE(H36:M36)</f>
         <v/>
       </c>
       <c r="V36">
-        <f>G36*N36</f>
-        <v/>
-      </c>
-      <c r="W36">
-        <f>G36*O36</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>SUM(P36:W36)</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>AVERAGE(H36:O36)</f>
-        <v/>
-      </c>
-      <c r="Z36">
-        <f>X36-G36*8</f>
+        <f>T36-G36*6</f>
         <v/>
       </c>
     </row>
@@ -13693,7 +12951,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -13713,54 +12971,40 @@
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
+      <c r="N37">
+        <f>G37*H37</f>
+        <v/>
+      </c>
+      <c r="O37">
+        <f>G37*I37</f>
+        <v/>
       </c>
       <c r="P37">
-        <f>G37*H37</f>
+        <f>G37*J37</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>G37*I37</f>
+        <f>G37*K37</f>
         <v/>
       </c>
       <c r="R37">
-        <f>G37*J37</f>
+        <f>G37*L37</f>
         <v/>
       </c>
       <c r="S37">
-        <f>G37*K37</f>
+        <f>G37*M37</f>
         <v/>
       </c>
       <c r="T37">
-        <f>G37*L37</f>
+        <f>SUM(N37:S37)</f>
         <v/>
       </c>
       <c r="U37">
-        <f>G37*M37</f>
+        <f>AVERAGE(H37:M37)</f>
         <v/>
       </c>
       <c r="V37">
-        <f>G37*N37</f>
-        <v/>
-      </c>
-      <c r="W37">
-        <f>G37*O37</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>SUM(P37:W37)</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>AVERAGE(H37:O37)</f>
-        <v/>
-      </c>
-      <c r="Z37">
-        <f>X37-G37*8</f>
+        <f>T37-G37*6</f>
         <v/>
       </c>
     </row>
@@ -13796,7 +13040,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -13816,54 +13060,40 @@
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
+      <c r="N38">
+        <f>G38*H38</f>
+        <v/>
+      </c>
+      <c r="O38">
+        <f>G38*I38</f>
+        <v/>
       </c>
       <c r="P38">
-        <f>G38*H38</f>
+        <f>G38*J38</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>G38*I38</f>
+        <f>G38*K38</f>
         <v/>
       </c>
       <c r="R38">
-        <f>G38*J38</f>
+        <f>G38*L38</f>
         <v/>
       </c>
       <c r="S38">
-        <f>G38*K38</f>
+        <f>G38*M38</f>
         <v/>
       </c>
       <c r="T38">
-        <f>G38*L38</f>
+        <f>SUM(N38:S38)</f>
         <v/>
       </c>
       <c r="U38">
-        <f>G38*M38</f>
+        <f>AVERAGE(H38:M38)</f>
         <v/>
       </c>
       <c r="V38">
-        <f>G38*N38</f>
-        <v/>
-      </c>
-      <c r="W38">
-        <f>G38*O38</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>SUM(P38:W38)</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>AVERAGE(H38:O38)</f>
-        <v/>
-      </c>
-      <c r="Z38">
-        <f>X38-G38*8</f>
+        <f>T38-G38*6</f>
         <v/>
       </c>
     </row>
@@ -13899,7 +13129,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -13919,54 +13149,40 @@
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
+      <c r="N39">
+        <f>G39*H39</f>
+        <v/>
+      </c>
+      <c r="O39">
+        <f>G39*I39</f>
+        <v/>
       </c>
       <c r="P39">
-        <f>G39*H39</f>
+        <f>G39*J39</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>G39*I39</f>
+        <f>G39*K39</f>
         <v/>
       </c>
       <c r="R39">
-        <f>G39*J39</f>
+        <f>G39*L39</f>
         <v/>
       </c>
       <c r="S39">
-        <f>G39*K39</f>
+        <f>G39*M39</f>
         <v/>
       </c>
       <c r="T39">
-        <f>G39*L39</f>
+        <f>SUM(N39:S39)</f>
         <v/>
       </c>
       <c r="U39">
-        <f>G39*M39</f>
+        <f>AVERAGE(H39:M39)</f>
         <v/>
       </c>
       <c r="V39">
-        <f>G39*N39</f>
-        <v/>
-      </c>
-      <c r="W39">
-        <f>G39*O39</f>
-        <v/>
-      </c>
-      <c r="X39">
-        <f>SUM(P39:W39)</f>
-        <v/>
-      </c>
-      <c r="Y39">
-        <f>AVERAGE(H39:O39)</f>
-        <v/>
-      </c>
-      <c r="Z39">
-        <f>X39-G39*8</f>
+        <f>T39-G39*6</f>
         <v/>
       </c>
     </row>
@@ -14002,7 +13218,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -14022,54 +13238,40 @@
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
+      <c r="N40">
+        <f>G40*H40</f>
+        <v/>
+      </c>
+      <c r="O40">
+        <f>G40*I40</f>
+        <v/>
       </c>
       <c r="P40">
-        <f>G40*H40</f>
+        <f>G40*J40</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>G40*I40</f>
+        <f>G40*K40</f>
         <v/>
       </c>
       <c r="R40">
-        <f>G40*J40</f>
+        <f>G40*L40</f>
         <v/>
       </c>
       <c r="S40">
-        <f>G40*K40</f>
+        <f>G40*M40</f>
         <v/>
       </c>
       <c r="T40">
-        <f>G40*L40</f>
+        <f>SUM(N40:S40)</f>
         <v/>
       </c>
       <c r="U40">
-        <f>G40*M40</f>
+        <f>AVERAGE(H40:M40)</f>
         <v/>
       </c>
       <c r="V40">
-        <f>G40*N40</f>
-        <v/>
-      </c>
-      <c r="W40">
-        <f>G40*O40</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>SUM(P40:W40)</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>AVERAGE(H40:O40)</f>
-        <v/>
-      </c>
-      <c r="Z40">
-        <f>X40-G40*8</f>
+        <f>T40-G40*6</f>
         <v/>
       </c>
     </row>
@@ -14105,7 +13307,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -14125,54 +13327,40 @@
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
+      <c r="N41">
+        <f>G41*H41</f>
+        <v/>
+      </c>
+      <c r="O41">
+        <f>G41*I41</f>
+        <v/>
       </c>
       <c r="P41">
-        <f>G41*H41</f>
+        <f>G41*J41</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>G41*I41</f>
+        <f>G41*K41</f>
         <v/>
       </c>
       <c r="R41">
-        <f>G41*J41</f>
+        <f>G41*L41</f>
         <v/>
       </c>
       <c r="S41">
-        <f>G41*K41</f>
+        <f>G41*M41</f>
         <v/>
       </c>
       <c r="T41">
-        <f>G41*L41</f>
+        <f>SUM(N41:S41)</f>
         <v/>
       </c>
       <c r="U41">
-        <f>G41*M41</f>
+        <f>AVERAGE(H41:M41)</f>
         <v/>
       </c>
       <c r="V41">
-        <f>G41*N41</f>
-        <v/>
-      </c>
-      <c r="W41">
-        <f>G41*O41</f>
-        <v/>
-      </c>
-      <c r="X41">
-        <f>SUM(P41:W41)</f>
-        <v/>
-      </c>
-      <c r="Y41">
-        <f>AVERAGE(H41:O41)</f>
-        <v/>
-      </c>
-      <c r="Z41">
-        <f>X41-G41*8</f>
+        <f>T41-G41*6</f>
         <v/>
       </c>
     </row>
@@ -14208,7 +13396,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -14228,54 +13416,40 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
+      <c r="N42">
+        <f>G42*H42</f>
+        <v/>
+      </c>
+      <c r="O42">
+        <f>G42*I42</f>
+        <v/>
       </c>
       <c r="P42">
-        <f>G42*H42</f>
+        <f>G42*J42</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>G42*I42</f>
+        <f>G42*K42</f>
         <v/>
       </c>
       <c r="R42">
-        <f>G42*J42</f>
+        <f>G42*L42</f>
         <v/>
       </c>
       <c r="S42">
-        <f>G42*K42</f>
+        <f>G42*M42</f>
         <v/>
       </c>
       <c r="T42">
-        <f>G42*L42</f>
+        <f>SUM(N42:S42)</f>
         <v/>
       </c>
       <c r="U42">
-        <f>G42*M42</f>
+        <f>AVERAGE(H42:M42)</f>
         <v/>
       </c>
       <c r="V42">
-        <f>G42*N42</f>
-        <v/>
-      </c>
-      <c r="W42">
-        <f>G42*O42</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>SUM(P42:W42)</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>AVERAGE(H42:O42)</f>
-        <v/>
-      </c>
-      <c r="Z42">
-        <f>X42-G42*8</f>
+        <f>T42-G42*6</f>
         <v/>
       </c>
     </row>
@@ -14311,7 +13485,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -14331,54 +13505,40 @@
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
+      <c r="N43">
+        <f>G43*H43</f>
+        <v/>
+      </c>
+      <c r="O43">
+        <f>G43*I43</f>
+        <v/>
       </c>
       <c r="P43">
-        <f>G43*H43</f>
+        <f>G43*J43</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>G43*I43</f>
+        <f>G43*K43</f>
         <v/>
       </c>
       <c r="R43">
-        <f>G43*J43</f>
+        <f>G43*L43</f>
         <v/>
       </c>
       <c r="S43">
-        <f>G43*K43</f>
+        <f>G43*M43</f>
         <v/>
       </c>
       <c r="T43">
-        <f>G43*L43</f>
+        <f>SUM(N43:S43)</f>
         <v/>
       </c>
       <c r="U43">
-        <f>G43*M43</f>
+        <f>AVERAGE(H43:M43)</f>
         <v/>
       </c>
       <c r="V43">
-        <f>G43*N43</f>
-        <v/>
-      </c>
-      <c r="W43">
-        <f>G43*O43</f>
-        <v/>
-      </c>
-      <c r="X43">
-        <f>SUM(P43:W43)</f>
-        <v/>
-      </c>
-      <c r="Y43">
-        <f>AVERAGE(H43:O43)</f>
-        <v/>
-      </c>
-      <c r="Z43">
-        <f>X43-G43*8</f>
+        <f>T43-G43*6</f>
         <v/>
       </c>
     </row>
@@ -14414,7 +13574,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -14434,54 +13594,40 @@
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
+      <c r="N44">
+        <f>G44*H44</f>
+        <v/>
+      </c>
+      <c r="O44">
+        <f>G44*I44</f>
+        <v/>
       </c>
       <c r="P44">
-        <f>G44*H44</f>
+        <f>G44*J44</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>G44*I44</f>
+        <f>G44*K44</f>
         <v/>
       </c>
       <c r="R44">
-        <f>G44*J44</f>
+        <f>G44*L44</f>
         <v/>
       </c>
       <c r="S44">
-        <f>G44*K44</f>
+        <f>G44*M44</f>
         <v/>
       </c>
       <c r="T44">
-        <f>G44*L44</f>
+        <f>SUM(N44:S44)</f>
         <v/>
       </c>
       <c r="U44">
-        <f>G44*M44</f>
+        <f>AVERAGE(H44:M44)</f>
         <v/>
       </c>
       <c r="V44">
-        <f>G44*N44</f>
-        <v/>
-      </c>
-      <c r="W44">
-        <f>G44*O44</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>SUM(P44:W44)</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>AVERAGE(H44:O44)</f>
-        <v/>
-      </c>
-      <c r="Z44">
-        <f>X44-G44*8</f>
+        <f>T44-G44*6</f>
         <v/>
       </c>
     </row>
@@ -14517,7 +13663,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -14537,54 +13683,40 @@
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
+      <c r="N45">
+        <f>G45*H45</f>
+        <v/>
+      </c>
+      <c r="O45">
+        <f>G45*I45</f>
+        <v/>
       </c>
       <c r="P45">
-        <f>G45*H45</f>
+        <f>G45*J45</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>G45*I45</f>
+        <f>G45*K45</f>
         <v/>
       </c>
       <c r="R45">
-        <f>G45*J45</f>
+        <f>G45*L45</f>
         <v/>
       </c>
       <c r="S45">
-        <f>G45*K45</f>
+        <f>G45*M45</f>
         <v/>
       </c>
       <c r="T45">
-        <f>G45*L45</f>
+        <f>SUM(N45:S45)</f>
         <v/>
       </c>
       <c r="U45">
-        <f>G45*M45</f>
+        <f>AVERAGE(H45:M45)</f>
         <v/>
       </c>
       <c r="V45">
-        <f>G45*N45</f>
-        <v/>
-      </c>
-      <c r="W45">
-        <f>G45*O45</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>SUM(P45:W45)</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>AVERAGE(H45:O45)</f>
-        <v/>
-      </c>
-      <c r="Z45">
-        <f>X45-G45*8</f>
+        <f>T45-G45*6</f>
         <v/>
       </c>
     </row>
@@ -14620,7 +13752,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -14640,54 +13772,40 @@
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
+      <c r="N46">
+        <f>G46*H46</f>
+        <v/>
+      </c>
+      <c r="O46">
+        <f>G46*I46</f>
+        <v/>
       </c>
       <c r="P46">
-        <f>G46*H46</f>
+        <f>G46*J46</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>G46*I46</f>
+        <f>G46*K46</f>
         <v/>
       </c>
       <c r="R46">
-        <f>G46*J46</f>
+        <f>G46*L46</f>
         <v/>
       </c>
       <c r="S46">
-        <f>G46*K46</f>
+        <f>G46*M46</f>
         <v/>
       </c>
       <c r="T46">
-        <f>G46*L46</f>
+        <f>SUM(N46:S46)</f>
         <v/>
       </c>
       <c r="U46">
-        <f>G46*M46</f>
+        <f>AVERAGE(H46:M46)</f>
         <v/>
       </c>
       <c r="V46">
-        <f>G46*N46</f>
-        <v/>
-      </c>
-      <c r="W46">
-        <f>G46*O46</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>SUM(P46:W46)</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>AVERAGE(H46:O46)</f>
-        <v/>
-      </c>
-      <c r="Z46">
-        <f>X46-G46*8</f>
+        <f>T46-G46*6</f>
         <v/>
       </c>
     </row>
@@ -14723,7 +13841,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -14743,54 +13861,40 @@
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
+      <c r="N47">
+        <f>G47*H47</f>
+        <v/>
+      </c>
+      <c r="O47">
+        <f>G47*I47</f>
+        <v/>
       </c>
       <c r="P47">
-        <f>G47*H47</f>
+        <f>G47*J47</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>G47*I47</f>
+        <f>G47*K47</f>
         <v/>
       </c>
       <c r="R47">
-        <f>G47*J47</f>
+        <f>G47*L47</f>
         <v/>
       </c>
       <c r="S47">
-        <f>G47*K47</f>
+        <f>G47*M47</f>
         <v/>
       </c>
       <c r="T47">
-        <f>G47*L47</f>
+        <f>SUM(N47:S47)</f>
         <v/>
       </c>
       <c r="U47">
-        <f>G47*M47</f>
+        <f>AVERAGE(H47:M47)</f>
         <v/>
       </c>
       <c r="V47">
-        <f>G47*N47</f>
-        <v/>
-      </c>
-      <c r="W47">
-        <f>G47*O47</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>SUM(P47:W47)</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>AVERAGE(H47:O47)</f>
-        <v/>
-      </c>
-      <c r="Z47">
-        <f>X47-G47*8</f>
+        <f>T47-G47*6</f>
         <v/>
       </c>
     </row>
@@ -14826,7 +13930,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -14846,54 +13950,40 @@
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
+      <c r="N48">
+        <f>G48*H48</f>
+        <v/>
+      </c>
+      <c r="O48">
+        <f>G48*I48</f>
+        <v/>
       </c>
       <c r="P48">
-        <f>G48*H48</f>
+        <f>G48*J48</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>G48*I48</f>
+        <f>G48*K48</f>
         <v/>
       </c>
       <c r="R48">
-        <f>G48*J48</f>
+        <f>G48*L48</f>
         <v/>
       </c>
       <c r="S48">
-        <f>G48*K48</f>
+        <f>G48*M48</f>
         <v/>
       </c>
       <c r="T48">
-        <f>G48*L48</f>
+        <f>SUM(N48:S48)</f>
         <v/>
       </c>
       <c r="U48">
-        <f>G48*M48</f>
+        <f>AVERAGE(H48:M48)</f>
         <v/>
       </c>
       <c r="V48">
-        <f>G48*N48</f>
-        <v/>
-      </c>
-      <c r="W48">
-        <f>G48*O48</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>SUM(P48:W48)</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>AVERAGE(H48:O48)</f>
-        <v/>
-      </c>
-      <c r="Z48">
-        <f>X48-G48*8</f>
+        <f>T48-G48*6</f>
         <v/>
       </c>
     </row>
@@ -14929,7 +14019,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -14949,54 +14039,40 @@
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
+      <c r="N49">
+        <f>G49*H49</f>
+        <v/>
+      </c>
+      <c r="O49">
+        <f>G49*I49</f>
+        <v/>
       </c>
       <c r="P49">
-        <f>G49*H49</f>
+        <f>G49*J49</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>G49*I49</f>
+        <f>G49*K49</f>
         <v/>
       </c>
       <c r="R49">
-        <f>G49*J49</f>
+        <f>G49*L49</f>
         <v/>
       </c>
       <c r="S49">
-        <f>G49*K49</f>
+        <f>G49*M49</f>
         <v/>
       </c>
       <c r="T49">
-        <f>G49*L49</f>
+        <f>SUM(N49:S49)</f>
         <v/>
       </c>
       <c r="U49">
-        <f>G49*M49</f>
+        <f>AVERAGE(H49:M49)</f>
         <v/>
       </c>
       <c r="V49">
-        <f>G49*N49</f>
-        <v/>
-      </c>
-      <c r="W49">
-        <f>G49*O49</f>
-        <v/>
-      </c>
-      <c r="X49">
-        <f>SUM(P49:W49)</f>
-        <v/>
-      </c>
-      <c r="Y49">
-        <f>AVERAGE(H49:O49)</f>
-        <v/>
-      </c>
-      <c r="Z49">
-        <f>X49-G49*8</f>
+        <f>T49-G49*6</f>
         <v/>
       </c>
     </row>
@@ -15032,7 +14108,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -15052,54 +14128,40 @@
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
+      <c r="N50">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="O50">
+        <f>G50*I50</f>
+        <v/>
       </c>
       <c r="P50">
-        <f>G50*H50</f>
+        <f>G50*J50</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>G50*I50</f>
+        <f>G50*K50</f>
         <v/>
       </c>
       <c r="R50">
-        <f>G50*J50</f>
+        <f>G50*L50</f>
         <v/>
       </c>
       <c r="S50">
-        <f>G50*K50</f>
+        <f>G50*M50</f>
         <v/>
       </c>
       <c r="T50">
-        <f>G50*L50</f>
+        <f>SUM(N50:S50)</f>
         <v/>
       </c>
       <c r="U50">
-        <f>G50*M50</f>
+        <f>AVERAGE(H50:M50)</f>
         <v/>
       </c>
       <c r="V50">
-        <f>G50*N50</f>
-        <v/>
-      </c>
-      <c r="W50">
-        <f>G50*O50</f>
-        <v/>
-      </c>
-      <c r="X50">
-        <f>SUM(P50:W50)</f>
-        <v/>
-      </c>
-      <c r="Y50">
-        <f>AVERAGE(H50:O50)</f>
-        <v/>
-      </c>
-      <c r="Z50">
-        <f>X50-G50*8</f>
+        <f>T50-G50*6</f>
         <v/>
       </c>
     </row>
@@ -15135,7 +14197,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -15155,54 +14217,40 @@
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
+      <c r="N51">
+        <f>G51*H51</f>
+        <v/>
+      </c>
+      <c r="O51">
+        <f>G51*I51</f>
+        <v/>
       </c>
       <c r="P51">
-        <f>G51*H51</f>
+        <f>G51*J51</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>G51*I51</f>
+        <f>G51*K51</f>
         <v/>
       </c>
       <c r="R51">
-        <f>G51*J51</f>
+        <f>G51*L51</f>
         <v/>
       </c>
       <c r="S51">
-        <f>G51*K51</f>
+        <f>G51*M51</f>
         <v/>
       </c>
       <c r="T51">
-        <f>G51*L51</f>
+        <f>SUM(N51:S51)</f>
         <v/>
       </c>
       <c r="U51">
-        <f>G51*M51</f>
+        <f>AVERAGE(H51:M51)</f>
         <v/>
       </c>
       <c r="V51">
-        <f>G51*N51</f>
-        <v/>
-      </c>
-      <c r="W51">
-        <f>G51*O51</f>
-        <v/>
-      </c>
-      <c r="X51">
-        <f>SUM(P51:W51)</f>
-        <v/>
-      </c>
-      <c r="Y51">
-        <f>AVERAGE(H51:O51)</f>
-        <v/>
-      </c>
-      <c r="Z51">
-        <f>X51-G51*8</f>
+        <f>T51-G51*6</f>
         <v/>
       </c>
     </row>
@@ -15238,7 +14286,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -15258,54 +14306,40 @@
       <c r="M52" t="n">
         <v>0</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
+      <c r="N52">
+        <f>G52*H52</f>
+        <v/>
+      </c>
+      <c r="O52">
+        <f>G52*I52</f>
+        <v/>
       </c>
       <c r="P52">
-        <f>G52*H52</f>
+        <f>G52*J52</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>G52*I52</f>
+        <f>G52*K52</f>
         <v/>
       </c>
       <c r="R52">
-        <f>G52*J52</f>
+        <f>G52*L52</f>
         <v/>
       </c>
       <c r="S52">
-        <f>G52*K52</f>
+        <f>G52*M52</f>
         <v/>
       </c>
       <c r="T52">
-        <f>G52*L52</f>
+        <f>SUM(N52:S52)</f>
         <v/>
       </c>
       <c r="U52">
-        <f>G52*M52</f>
+        <f>AVERAGE(H52:M52)</f>
         <v/>
       </c>
       <c r="V52">
-        <f>G52*N52</f>
-        <v/>
-      </c>
-      <c r="W52">
-        <f>G52*O52</f>
-        <v/>
-      </c>
-      <c r="X52">
-        <f>SUM(P52:W52)</f>
-        <v/>
-      </c>
-      <c r="Y52">
-        <f>AVERAGE(H52:O52)</f>
-        <v/>
-      </c>
-      <c r="Z52">
-        <f>X52-G52*8</f>
+        <f>T52-G52*6</f>
         <v/>
       </c>
     </row>
@@ -15341,7 +14375,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -15361,54 +14395,40 @@
       <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
+      <c r="N53">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="O53">
+        <f>G53*I53</f>
+        <v/>
       </c>
       <c r="P53">
-        <f>G53*H53</f>
+        <f>G53*J53</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>G53*I53</f>
+        <f>G53*K53</f>
         <v/>
       </c>
       <c r="R53">
-        <f>G53*J53</f>
+        <f>G53*L53</f>
         <v/>
       </c>
       <c r="S53">
-        <f>G53*K53</f>
+        <f>G53*M53</f>
         <v/>
       </c>
       <c r="T53">
-        <f>G53*L53</f>
+        <f>SUM(N53:S53)</f>
         <v/>
       </c>
       <c r="U53">
-        <f>G53*M53</f>
+        <f>AVERAGE(H53:M53)</f>
         <v/>
       </c>
       <c r="V53">
-        <f>G53*N53</f>
-        <v/>
-      </c>
-      <c r="W53">
-        <f>G53*O53</f>
-        <v/>
-      </c>
-      <c r="X53">
-        <f>SUM(P53:W53)</f>
-        <v/>
-      </c>
-      <c r="Y53">
-        <f>AVERAGE(H53:O53)</f>
-        <v/>
-      </c>
-      <c r="Z53">
-        <f>X53-G53*8</f>
+        <f>T53-G53*6</f>
         <v/>
       </c>
     </row>
@@ -15444,7 +14464,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -15464,54 +14484,40 @@
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
+      <c r="N54">
+        <f>G54*H54</f>
+        <v/>
+      </c>
+      <c r="O54">
+        <f>G54*I54</f>
+        <v/>
       </c>
       <c r="P54">
-        <f>G54*H54</f>
+        <f>G54*J54</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>G54*I54</f>
+        <f>G54*K54</f>
         <v/>
       </c>
       <c r="R54">
-        <f>G54*J54</f>
+        <f>G54*L54</f>
         <v/>
       </c>
       <c r="S54">
-        <f>G54*K54</f>
+        <f>G54*M54</f>
         <v/>
       </c>
       <c r="T54">
-        <f>G54*L54</f>
+        <f>SUM(N54:S54)</f>
         <v/>
       </c>
       <c r="U54">
-        <f>G54*M54</f>
+        <f>AVERAGE(H54:M54)</f>
         <v/>
       </c>
       <c r="V54">
-        <f>G54*N54</f>
-        <v/>
-      </c>
-      <c r="W54">
-        <f>G54*O54</f>
-        <v/>
-      </c>
-      <c r="X54">
-        <f>SUM(P54:W54)</f>
-        <v/>
-      </c>
-      <c r="Y54">
-        <f>AVERAGE(H54:O54)</f>
-        <v/>
-      </c>
-      <c r="Z54">
-        <f>X54-G54*8</f>
+        <f>T54-G54*6</f>
         <v/>
       </c>
     </row>
@@ -15547,7 +14553,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -15567,54 +14573,40 @@
       <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
+      <c r="N55">
+        <f>G55*H55</f>
+        <v/>
+      </c>
+      <c r="O55">
+        <f>G55*I55</f>
+        <v/>
       </c>
       <c r="P55">
-        <f>G55*H55</f>
+        <f>G55*J55</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>G55*I55</f>
+        <f>G55*K55</f>
         <v/>
       </c>
       <c r="R55">
-        <f>G55*J55</f>
+        <f>G55*L55</f>
         <v/>
       </c>
       <c r="S55">
-        <f>G55*K55</f>
+        <f>G55*M55</f>
         <v/>
       </c>
       <c r="T55">
-        <f>G55*L55</f>
+        <f>SUM(N55:S55)</f>
         <v/>
       </c>
       <c r="U55">
-        <f>G55*M55</f>
+        <f>AVERAGE(H55:M55)</f>
         <v/>
       </c>
       <c r="V55">
-        <f>G55*N55</f>
-        <v/>
-      </c>
-      <c r="W55">
-        <f>G55*O55</f>
-        <v/>
-      </c>
-      <c r="X55">
-        <f>SUM(P55:W55)</f>
-        <v/>
-      </c>
-      <c r="Y55">
-        <f>AVERAGE(H55:O55)</f>
-        <v/>
-      </c>
-      <c r="Z55">
-        <f>X55-G55*8</f>
+        <f>T55-G55*6</f>
         <v/>
       </c>
     </row>
@@ -15650,7 +14642,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -15670,54 +14662,40 @@
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
+      <c r="N56">
+        <f>G56*H56</f>
+        <v/>
+      </c>
+      <c r="O56">
+        <f>G56*I56</f>
+        <v/>
       </c>
       <c r="P56">
-        <f>G56*H56</f>
+        <f>G56*J56</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>G56*I56</f>
+        <f>G56*K56</f>
         <v/>
       </c>
       <c r="R56">
-        <f>G56*J56</f>
+        <f>G56*L56</f>
         <v/>
       </c>
       <c r="S56">
-        <f>G56*K56</f>
+        <f>G56*M56</f>
         <v/>
       </c>
       <c r="T56">
-        <f>G56*L56</f>
+        <f>SUM(N56:S56)</f>
         <v/>
       </c>
       <c r="U56">
-        <f>G56*M56</f>
+        <f>AVERAGE(H56:M56)</f>
         <v/>
       </c>
       <c r="V56">
-        <f>G56*N56</f>
-        <v/>
-      </c>
-      <c r="W56">
-        <f>G56*O56</f>
-        <v/>
-      </c>
-      <c r="X56">
-        <f>SUM(P56:W56)</f>
-        <v/>
-      </c>
-      <c r="Y56">
-        <f>AVERAGE(H56:O56)</f>
-        <v/>
-      </c>
-      <c r="Z56">
-        <f>X56-G56*8</f>
+        <f>T56-G56*6</f>
         <v/>
       </c>
     </row>
@@ -15753,7 +14731,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -15773,54 +14751,40 @@
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
+      <c r="N57">
+        <f>G57*H57</f>
+        <v/>
+      </c>
+      <c r="O57">
+        <f>G57*I57</f>
+        <v/>
       </c>
       <c r="P57">
-        <f>G57*H57</f>
+        <f>G57*J57</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>G57*I57</f>
+        <f>G57*K57</f>
         <v/>
       </c>
       <c r="R57">
-        <f>G57*J57</f>
+        <f>G57*L57</f>
         <v/>
       </c>
       <c r="S57">
-        <f>G57*K57</f>
+        <f>G57*M57</f>
         <v/>
       </c>
       <c r="T57">
-        <f>G57*L57</f>
+        <f>SUM(N57:S57)</f>
         <v/>
       </c>
       <c r="U57">
-        <f>G57*M57</f>
+        <f>AVERAGE(H57:M57)</f>
         <v/>
       </c>
       <c r="V57">
-        <f>G57*N57</f>
-        <v/>
-      </c>
-      <c r="W57">
-        <f>G57*O57</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>SUM(P57:W57)</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>AVERAGE(H57:O57)</f>
-        <v/>
-      </c>
-      <c r="Z57">
-        <f>X57-G57*8</f>
+        <f>T57-G57*6</f>
         <v/>
       </c>
     </row>
@@ -15856,7 +14820,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -15876,54 +14840,40 @@
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
+      <c r="N58">
+        <f>G58*H58</f>
+        <v/>
+      </c>
+      <c r="O58">
+        <f>G58*I58</f>
+        <v/>
       </c>
       <c r="P58">
-        <f>G58*H58</f>
+        <f>G58*J58</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>G58*I58</f>
+        <f>G58*K58</f>
         <v/>
       </c>
       <c r="R58">
-        <f>G58*J58</f>
+        <f>G58*L58</f>
         <v/>
       </c>
       <c r="S58">
-        <f>G58*K58</f>
+        <f>G58*M58</f>
         <v/>
       </c>
       <c r="T58">
-        <f>G58*L58</f>
+        <f>SUM(N58:S58)</f>
         <v/>
       </c>
       <c r="U58">
-        <f>G58*M58</f>
+        <f>AVERAGE(H58:M58)</f>
         <v/>
       </c>
       <c r="V58">
-        <f>G58*N58</f>
-        <v/>
-      </c>
-      <c r="W58">
-        <f>G58*O58</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>SUM(P58:W58)</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>AVERAGE(H58:O58)</f>
-        <v/>
-      </c>
-      <c r="Z58">
-        <f>X58-G58*8</f>
+        <f>T58-G58*6</f>
         <v/>
       </c>
     </row>
@@ -15959,7 +14909,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -15979,54 +14929,40 @@
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
+      <c r="N59">
+        <f>G59*H59</f>
+        <v/>
+      </c>
+      <c r="O59">
+        <f>G59*I59</f>
+        <v/>
       </c>
       <c r="P59">
-        <f>G59*H59</f>
+        <f>G59*J59</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>G59*I59</f>
+        <f>G59*K59</f>
         <v/>
       </c>
       <c r="R59">
-        <f>G59*J59</f>
+        <f>G59*L59</f>
         <v/>
       </c>
       <c r="S59">
-        <f>G59*K59</f>
+        <f>G59*M59</f>
         <v/>
       </c>
       <c r="T59">
-        <f>G59*L59</f>
+        <f>SUM(N59:S59)</f>
         <v/>
       </c>
       <c r="U59">
-        <f>G59*M59</f>
+        <f>AVERAGE(H59:M59)</f>
         <v/>
       </c>
       <c r="V59">
-        <f>G59*N59</f>
-        <v/>
-      </c>
-      <c r="W59">
-        <f>G59*O59</f>
-        <v/>
-      </c>
-      <c r="X59">
-        <f>SUM(P59:W59)</f>
-        <v/>
-      </c>
-      <c r="Y59">
-        <f>AVERAGE(H59:O59)</f>
-        <v/>
-      </c>
-      <c r="Z59">
-        <f>X59-G59*8</f>
+        <f>T59-G59*6</f>
         <v/>
       </c>
     </row>
@@ -16062,7 +14998,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -16082,54 +15018,40 @@
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
+      <c r="N60">
+        <f>G60*H60</f>
+        <v/>
+      </c>
+      <c r="O60">
+        <f>G60*I60</f>
+        <v/>
       </c>
       <c r="P60">
-        <f>G60*H60</f>
+        <f>G60*J60</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>G60*I60</f>
+        <f>G60*K60</f>
         <v/>
       </c>
       <c r="R60">
-        <f>G60*J60</f>
+        <f>G60*L60</f>
         <v/>
       </c>
       <c r="S60">
-        <f>G60*K60</f>
+        <f>G60*M60</f>
         <v/>
       </c>
       <c r="T60">
-        <f>G60*L60</f>
+        <f>SUM(N60:S60)</f>
         <v/>
       </c>
       <c r="U60">
-        <f>G60*M60</f>
+        <f>AVERAGE(H60:M60)</f>
         <v/>
       </c>
       <c r="V60">
-        <f>G60*N60</f>
-        <v/>
-      </c>
-      <c r="W60">
-        <f>G60*O60</f>
-        <v/>
-      </c>
-      <c r="X60">
-        <f>SUM(P60:W60)</f>
-        <v/>
-      </c>
-      <c r="Y60">
-        <f>AVERAGE(H60:O60)</f>
-        <v/>
-      </c>
-      <c r="Z60">
-        <f>X60-G60*8</f>
+        <f>T60-G60*6</f>
         <v/>
       </c>
     </row>
@@ -16165,7 +15087,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -16185,54 +15107,40 @@
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
+      <c r="N61">
+        <f>G61*H61</f>
+        <v/>
+      </c>
+      <c r="O61">
+        <f>G61*I61</f>
+        <v/>
       </c>
       <c r="P61">
-        <f>G61*H61</f>
+        <f>G61*J61</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>G61*I61</f>
+        <f>G61*K61</f>
         <v/>
       </c>
       <c r="R61">
-        <f>G61*J61</f>
+        <f>G61*L61</f>
         <v/>
       </c>
       <c r="S61">
-        <f>G61*K61</f>
+        <f>G61*M61</f>
         <v/>
       </c>
       <c r="T61">
-        <f>G61*L61</f>
+        <f>SUM(N61:S61)</f>
         <v/>
       </c>
       <c r="U61">
-        <f>G61*M61</f>
+        <f>AVERAGE(H61:M61)</f>
         <v/>
       </c>
       <c r="V61">
-        <f>G61*N61</f>
-        <v/>
-      </c>
-      <c r="W61">
-        <f>G61*O61</f>
-        <v/>
-      </c>
-      <c r="X61">
-        <f>SUM(P61:W61)</f>
-        <v/>
-      </c>
-      <c r="Y61">
-        <f>AVERAGE(H61:O61)</f>
-        <v/>
-      </c>
-      <c r="Z61">
-        <f>X61-G61*8</f>
+        <f>T61-G61*6</f>
         <v/>
       </c>
     </row>
@@ -16268,7 +15176,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -16288,54 +15196,40 @@
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
+      <c r="N62">
+        <f>G62*H62</f>
+        <v/>
+      </c>
+      <c r="O62">
+        <f>G62*I62</f>
+        <v/>
       </c>
       <c r="P62">
-        <f>G62*H62</f>
+        <f>G62*J62</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>G62*I62</f>
+        <f>G62*K62</f>
         <v/>
       </c>
       <c r="R62">
-        <f>G62*J62</f>
+        <f>G62*L62</f>
         <v/>
       </c>
       <c r="S62">
-        <f>G62*K62</f>
+        <f>G62*M62</f>
         <v/>
       </c>
       <c r="T62">
-        <f>G62*L62</f>
+        <f>SUM(N62:S62)</f>
         <v/>
       </c>
       <c r="U62">
-        <f>G62*M62</f>
+        <f>AVERAGE(H62:M62)</f>
         <v/>
       </c>
       <c r="V62">
-        <f>G62*N62</f>
-        <v/>
-      </c>
-      <c r="W62">
-        <f>G62*O62</f>
-        <v/>
-      </c>
-      <c r="X62">
-        <f>SUM(P62:W62)</f>
-        <v/>
-      </c>
-      <c r="Y62">
-        <f>AVERAGE(H62:O62)</f>
-        <v/>
-      </c>
-      <c r="Z62">
-        <f>X62-G62*8</f>
+        <f>T62-G62*6</f>
         <v/>
       </c>
     </row>
@@ -16371,7 +15265,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -16391,54 +15285,40 @@
       <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
+      <c r="N63">
+        <f>G63*H63</f>
+        <v/>
+      </c>
+      <c r="O63">
+        <f>G63*I63</f>
+        <v/>
       </c>
       <c r="P63">
-        <f>G63*H63</f>
+        <f>G63*J63</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>G63*I63</f>
+        <f>G63*K63</f>
         <v/>
       </c>
       <c r="R63">
-        <f>G63*J63</f>
+        <f>G63*L63</f>
         <v/>
       </c>
       <c r="S63">
-        <f>G63*K63</f>
+        <f>G63*M63</f>
         <v/>
       </c>
       <c r="T63">
-        <f>G63*L63</f>
+        <f>SUM(N63:S63)</f>
         <v/>
       </c>
       <c r="U63">
-        <f>G63*M63</f>
+        <f>AVERAGE(H63:M63)</f>
         <v/>
       </c>
       <c r="V63">
-        <f>G63*N63</f>
-        <v/>
-      </c>
-      <c r="W63">
-        <f>G63*O63</f>
-        <v/>
-      </c>
-      <c r="X63">
-        <f>SUM(P63:W63)</f>
-        <v/>
-      </c>
-      <c r="Y63">
-        <f>AVERAGE(H63:O63)</f>
-        <v/>
-      </c>
-      <c r="Z63">
-        <f>X63-G63*8</f>
+        <f>T63-G63*6</f>
         <v/>
       </c>
     </row>
@@ -16474,7 +15354,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -16494,54 +15374,40 @@
       <c r="M64" t="n">
         <v>0</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
+      <c r="N64">
+        <f>G64*H64</f>
+        <v/>
+      </c>
+      <c r="O64">
+        <f>G64*I64</f>
+        <v/>
       </c>
       <c r="P64">
-        <f>G64*H64</f>
+        <f>G64*J64</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>G64*I64</f>
+        <f>G64*K64</f>
         <v/>
       </c>
       <c r="R64">
-        <f>G64*J64</f>
+        <f>G64*L64</f>
         <v/>
       </c>
       <c r="S64">
-        <f>G64*K64</f>
+        <f>G64*M64</f>
         <v/>
       </c>
       <c r="T64">
-        <f>G64*L64</f>
+        <f>SUM(N64:S64)</f>
         <v/>
       </c>
       <c r="U64">
-        <f>G64*M64</f>
+        <f>AVERAGE(H64:M64)</f>
         <v/>
       </c>
       <c r="V64">
-        <f>G64*N64</f>
-        <v/>
-      </c>
-      <c r="W64">
-        <f>G64*O64</f>
-        <v/>
-      </c>
-      <c r="X64">
-        <f>SUM(P64:W64)</f>
-        <v/>
-      </c>
-      <c r="Y64">
-        <f>AVERAGE(H64:O64)</f>
-        <v/>
-      </c>
-      <c r="Z64">
-        <f>X64-G64*8</f>
+        <f>T64-G64*6</f>
         <v/>
       </c>
     </row>
@@ -16577,7 +15443,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -16597,54 +15463,40 @@
       <c r="M65" t="n">
         <v>0</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
+      <c r="N65">
+        <f>G65*H65</f>
+        <v/>
+      </c>
+      <c r="O65">
+        <f>G65*I65</f>
+        <v/>
       </c>
       <c r="P65">
-        <f>G65*H65</f>
+        <f>G65*J65</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>G65*I65</f>
+        <f>G65*K65</f>
         <v/>
       </c>
       <c r="R65">
-        <f>G65*J65</f>
+        <f>G65*L65</f>
         <v/>
       </c>
       <c r="S65">
-        <f>G65*K65</f>
+        <f>G65*M65</f>
         <v/>
       </c>
       <c r="T65">
-        <f>G65*L65</f>
+        <f>SUM(N65:S65)</f>
         <v/>
       </c>
       <c r="U65">
-        <f>G65*M65</f>
+        <f>AVERAGE(H65:M65)</f>
         <v/>
       </c>
       <c r="V65">
-        <f>G65*N65</f>
-        <v/>
-      </c>
-      <c r="W65">
-        <f>G65*O65</f>
-        <v/>
-      </c>
-      <c r="X65">
-        <f>SUM(P65:W65)</f>
-        <v/>
-      </c>
-      <c r="Y65">
-        <f>AVERAGE(H65:O65)</f>
-        <v/>
-      </c>
-      <c r="Z65">
-        <f>X65-G65*8</f>
+        <f>T65-G65*6</f>
         <v/>
       </c>
     </row>
@@ -16680,7 +15532,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -16700,54 +15552,40 @@
       <c r="M66" t="n">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
+      <c r="N66">
+        <f>G66*H66</f>
+        <v/>
+      </c>
+      <c r="O66">
+        <f>G66*I66</f>
+        <v/>
       </c>
       <c r="P66">
-        <f>G66*H66</f>
+        <f>G66*J66</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>G66*I66</f>
+        <f>G66*K66</f>
         <v/>
       </c>
       <c r="R66">
-        <f>G66*J66</f>
+        <f>G66*L66</f>
         <v/>
       </c>
       <c r="S66">
-        <f>G66*K66</f>
+        <f>G66*M66</f>
         <v/>
       </c>
       <c r="T66">
-        <f>G66*L66</f>
+        <f>SUM(N66:S66)</f>
         <v/>
       </c>
       <c r="U66">
-        <f>G66*M66</f>
+        <f>AVERAGE(H66:M66)</f>
         <v/>
       </c>
       <c r="V66">
-        <f>G66*N66</f>
-        <v/>
-      </c>
-      <c r="W66">
-        <f>G66*O66</f>
-        <v/>
-      </c>
-      <c r="X66">
-        <f>SUM(P66:W66)</f>
-        <v/>
-      </c>
-      <c r="Y66">
-        <f>AVERAGE(H66:O66)</f>
-        <v/>
-      </c>
-      <c r="Z66">
-        <f>X66-G66*8</f>
+        <f>T66-G66*6</f>
         <v/>
       </c>
     </row>
@@ -16783,7 +15621,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -16803,54 +15641,40 @@
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
+      <c r="N67">
+        <f>G67*H67</f>
+        <v/>
+      </c>
+      <c r="O67">
+        <f>G67*I67</f>
+        <v/>
       </c>
       <c r="P67">
-        <f>G67*H67</f>
+        <f>G67*J67</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>G67*I67</f>
+        <f>G67*K67</f>
         <v/>
       </c>
       <c r="R67">
-        <f>G67*J67</f>
+        <f>G67*L67</f>
         <v/>
       </c>
       <c r="S67">
-        <f>G67*K67</f>
+        <f>G67*M67</f>
         <v/>
       </c>
       <c r="T67">
-        <f>G67*L67</f>
+        <f>SUM(N67:S67)</f>
         <v/>
       </c>
       <c r="U67">
-        <f>G67*M67</f>
+        <f>AVERAGE(H67:M67)</f>
         <v/>
       </c>
       <c r="V67">
-        <f>G67*N67</f>
-        <v/>
-      </c>
-      <c r="W67">
-        <f>G67*O67</f>
-        <v/>
-      </c>
-      <c r="X67">
-        <f>SUM(P67:W67)</f>
-        <v/>
-      </c>
-      <c r="Y67">
-        <f>AVERAGE(H67:O67)</f>
-        <v/>
-      </c>
-      <c r="Z67">
-        <f>X67-G67*8</f>
+        <f>T67-G67*6</f>
         <v/>
       </c>
     </row>
@@ -16886,7 +15710,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -16906,54 +15730,40 @@
       <c r="M68" t="n">
         <v>0</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
+      <c r="N68">
+        <f>G68*H68</f>
+        <v/>
+      </c>
+      <c r="O68">
+        <f>G68*I68</f>
+        <v/>
       </c>
       <c r="P68">
-        <f>G68*H68</f>
+        <f>G68*J68</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>G68*I68</f>
+        <f>G68*K68</f>
         <v/>
       </c>
       <c r="R68">
-        <f>G68*J68</f>
+        <f>G68*L68</f>
         <v/>
       </c>
       <c r="S68">
-        <f>G68*K68</f>
+        <f>G68*M68</f>
         <v/>
       </c>
       <c r="T68">
-        <f>G68*L68</f>
+        <f>SUM(N68:S68)</f>
         <v/>
       </c>
       <c r="U68">
-        <f>G68*M68</f>
+        <f>AVERAGE(H68:M68)</f>
         <v/>
       </c>
       <c r="V68">
-        <f>G68*N68</f>
-        <v/>
-      </c>
-      <c r="W68">
-        <f>G68*O68</f>
-        <v/>
-      </c>
-      <c r="X68">
-        <f>SUM(P68:W68)</f>
-        <v/>
-      </c>
-      <c r="Y68">
-        <f>AVERAGE(H68:O68)</f>
-        <v/>
-      </c>
-      <c r="Z68">
-        <f>X68-G68*8</f>
+        <f>T68-G68*6</f>
         <v/>
       </c>
     </row>
@@ -16989,7 +15799,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -17009,54 +15819,40 @@
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
+      <c r="N69">
+        <f>G69*H69</f>
+        <v/>
+      </c>
+      <c r="O69">
+        <f>G69*I69</f>
+        <v/>
       </c>
       <c r="P69">
-        <f>G69*H69</f>
+        <f>G69*J69</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>G69*I69</f>
+        <f>G69*K69</f>
         <v/>
       </c>
       <c r="R69">
-        <f>G69*J69</f>
+        <f>G69*L69</f>
         <v/>
       </c>
       <c r="S69">
-        <f>G69*K69</f>
+        <f>G69*M69</f>
         <v/>
       </c>
       <c r="T69">
-        <f>G69*L69</f>
+        <f>SUM(N69:S69)</f>
         <v/>
       </c>
       <c r="U69">
-        <f>G69*M69</f>
+        <f>AVERAGE(H69:M69)</f>
         <v/>
       </c>
       <c r="V69">
-        <f>G69*N69</f>
-        <v/>
-      </c>
-      <c r="W69">
-        <f>G69*O69</f>
-        <v/>
-      </c>
-      <c r="X69">
-        <f>SUM(P69:W69)</f>
-        <v/>
-      </c>
-      <c r="Y69">
-        <f>AVERAGE(H69:O69)</f>
-        <v/>
-      </c>
-      <c r="Z69">
-        <f>X69-G69*8</f>
+        <f>T69-G69*6</f>
         <v/>
       </c>
     </row>
@@ -17092,7 +15888,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -17112,54 +15908,40 @@
       <c r="M70" t="n">
         <v>0</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
+      <c r="N70">
+        <f>G70*H70</f>
+        <v/>
+      </c>
+      <c r="O70">
+        <f>G70*I70</f>
+        <v/>
       </c>
       <c r="P70">
-        <f>G70*H70</f>
+        <f>G70*J70</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>G70*I70</f>
+        <f>G70*K70</f>
         <v/>
       </c>
       <c r="R70">
-        <f>G70*J70</f>
+        <f>G70*L70</f>
         <v/>
       </c>
       <c r="S70">
-        <f>G70*K70</f>
+        <f>G70*M70</f>
         <v/>
       </c>
       <c r="T70">
-        <f>G70*L70</f>
+        <f>SUM(N70:S70)</f>
         <v/>
       </c>
       <c r="U70">
-        <f>G70*M70</f>
+        <f>AVERAGE(H70:M70)</f>
         <v/>
       </c>
       <c r="V70">
-        <f>G70*N70</f>
-        <v/>
-      </c>
-      <c r="W70">
-        <f>G70*O70</f>
-        <v/>
-      </c>
-      <c r="X70">
-        <f>SUM(P70:W70)</f>
-        <v/>
-      </c>
-      <c r="Y70">
-        <f>AVERAGE(H70:O70)</f>
-        <v/>
-      </c>
-      <c r="Z70">
-        <f>X70-G70*8</f>
+        <f>T70-G70*6</f>
         <v/>
       </c>
     </row>
@@ -17195,7 +15977,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -17215,54 +15997,40 @@
       <c r="M71" t="n">
         <v>0</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
+      <c r="N71">
+        <f>G71*H71</f>
+        <v/>
+      </c>
+      <c r="O71">
+        <f>G71*I71</f>
+        <v/>
       </c>
       <c r="P71">
-        <f>G71*H71</f>
+        <f>G71*J71</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>G71*I71</f>
+        <f>G71*K71</f>
         <v/>
       </c>
       <c r="R71">
-        <f>G71*J71</f>
+        <f>G71*L71</f>
         <v/>
       </c>
       <c r="S71">
-        <f>G71*K71</f>
+        <f>G71*M71</f>
         <v/>
       </c>
       <c r="T71">
-        <f>G71*L71</f>
+        <f>SUM(N71:S71)</f>
         <v/>
       </c>
       <c r="U71">
-        <f>G71*M71</f>
+        <f>AVERAGE(H71:M71)</f>
         <v/>
       </c>
       <c r="V71">
-        <f>G71*N71</f>
-        <v/>
-      </c>
-      <c r="W71">
-        <f>G71*O71</f>
-        <v/>
-      </c>
-      <c r="X71">
-        <f>SUM(P71:W71)</f>
-        <v/>
-      </c>
-      <c r="Y71">
-        <f>AVERAGE(H71:O71)</f>
-        <v/>
-      </c>
-      <c r="Z71">
-        <f>X71-G71*8</f>
+        <f>T71-G71*6</f>
         <v/>
       </c>
     </row>
@@ -17298,7 +16066,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -17318,54 +16086,40 @@
       <c r="M72" t="n">
         <v>0</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
+      <c r="N72">
+        <f>G72*H72</f>
+        <v/>
+      </c>
+      <c r="O72">
+        <f>G72*I72</f>
+        <v/>
       </c>
       <c r="P72">
-        <f>G72*H72</f>
+        <f>G72*J72</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>G72*I72</f>
+        <f>G72*K72</f>
         <v/>
       </c>
       <c r="R72">
-        <f>G72*J72</f>
+        <f>G72*L72</f>
         <v/>
       </c>
       <c r="S72">
-        <f>G72*K72</f>
+        <f>G72*M72</f>
         <v/>
       </c>
       <c r="T72">
-        <f>G72*L72</f>
+        <f>SUM(N72:S72)</f>
         <v/>
       </c>
       <c r="U72">
-        <f>G72*M72</f>
+        <f>AVERAGE(H72:M72)</f>
         <v/>
       </c>
       <c r="V72">
-        <f>G72*N72</f>
-        <v/>
-      </c>
-      <c r="W72">
-        <f>G72*O72</f>
-        <v/>
-      </c>
-      <c r="X72">
-        <f>SUM(P72:W72)</f>
-        <v/>
-      </c>
-      <c r="Y72">
-        <f>AVERAGE(H72:O72)</f>
-        <v/>
-      </c>
-      <c r="Z72">
-        <f>X72-G72*8</f>
+        <f>T72-G72*6</f>
         <v/>
       </c>
     </row>
@@ -17401,7 +16155,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -17421,54 +16175,40 @@
       <c r="M73" t="n">
         <v>0</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
+      <c r="N73">
+        <f>G73*H73</f>
+        <v/>
+      </c>
+      <c r="O73">
+        <f>G73*I73</f>
+        <v/>
       </c>
       <c r="P73">
-        <f>G73*H73</f>
+        <f>G73*J73</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>G73*I73</f>
+        <f>G73*K73</f>
         <v/>
       </c>
       <c r="R73">
-        <f>G73*J73</f>
+        <f>G73*L73</f>
         <v/>
       </c>
       <c r="S73">
-        <f>G73*K73</f>
+        <f>G73*M73</f>
         <v/>
       </c>
       <c r="T73">
-        <f>G73*L73</f>
+        <f>SUM(N73:S73)</f>
         <v/>
       </c>
       <c r="U73">
-        <f>G73*M73</f>
+        <f>AVERAGE(H73:M73)</f>
         <v/>
       </c>
       <c r="V73">
-        <f>G73*N73</f>
-        <v/>
-      </c>
-      <c r="W73">
-        <f>G73*O73</f>
-        <v/>
-      </c>
-      <c r="X73">
-        <f>SUM(P73:W73)</f>
-        <v/>
-      </c>
-      <c r="Y73">
-        <f>AVERAGE(H73:O73)</f>
-        <v/>
-      </c>
-      <c r="Z73">
-        <f>X73-G73*8</f>
+        <f>T73-G73*6</f>
         <v/>
       </c>
     </row>
@@ -17504,7 +16244,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -17524,54 +16264,40 @@
       <c r="M74" t="n">
         <v>0</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
+      <c r="N74">
+        <f>G74*H74</f>
+        <v/>
+      </c>
+      <c r="O74">
+        <f>G74*I74</f>
+        <v/>
       </c>
       <c r="P74">
-        <f>G74*H74</f>
+        <f>G74*J74</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>G74*I74</f>
+        <f>G74*K74</f>
         <v/>
       </c>
       <c r="R74">
-        <f>G74*J74</f>
+        <f>G74*L74</f>
         <v/>
       </c>
       <c r="S74">
-        <f>G74*K74</f>
+        <f>G74*M74</f>
         <v/>
       </c>
       <c r="T74">
-        <f>G74*L74</f>
+        <f>SUM(N74:S74)</f>
         <v/>
       </c>
       <c r="U74">
-        <f>G74*M74</f>
+        <f>AVERAGE(H74:M74)</f>
         <v/>
       </c>
       <c r="V74">
-        <f>G74*N74</f>
-        <v/>
-      </c>
-      <c r="W74">
-        <f>G74*O74</f>
-        <v/>
-      </c>
-      <c r="X74">
-        <f>SUM(P74:W74)</f>
-        <v/>
-      </c>
-      <c r="Y74">
-        <f>AVERAGE(H74:O74)</f>
-        <v/>
-      </c>
-      <c r="Z74">
-        <f>X74-G74*8</f>
+        <f>T74-G74*6</f>
         <v/>
       </c>
     </row>
@@ -17607,7 +16333,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -17627,54 +16353,40 @@
       <c r="M75" t="n">
         <v>0</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
+      <c r="N75">
+        <f>G75*H75</f>
+        <v/>
+      </c>
+      <c r="O75">
+        <f>G75*I75</f>
+        <v/>
       </c>
       <c r="P75">
-        <f>G75*H75</f>
+        <f>G75*J75</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>G75*I75</f>
+        <f>G75*K75</f>
         <v/>
       </c>
       <c r="R75">
-        <f>G75*J75</f>
+        <f>G75*L75</f>
         <v/>
       </c>
       <c r="S75">
-        <f>G75*K75</f>
+        <f>G75*M75</f>
         <v/>
       </c>
       <c r="T75">
-        <f>G75*L75</f>
+        <f>SUM(N75:S75)</f>
         <v/>
       </c>
       <c r="U75">
-        <f>G75*M75</f>
+        <f>AVERAGE(H75:M75)</f>
         <v/>
       </c>
       <c r="V75">
-        <f>G75*N75</f>
-        <v/>
-      </c>
-      <c r="W75">
-        <f>G75*O75</f>
-        <v/>
-      </c>
-      <c r="X75">
-        <f>SUM(P75:W75)</f>
-        <v/>
-      </c>
-      <c r="Y75">
-        <f>AVERAGE(H75:O75)</f>
-        <v/>
-      </c>
-      <c r="Z75">
-        <f>X75-G75*8</f>
+        <f>T75-G75*6</f>
         <v/>
       </c>
     </row>
@@ -17710,7 +16422,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -17730,54 +16442,40 @@
       <c r="M76" t="n">
         <v>0</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
+      <c r="N76">
+        <f>G76*H76</f>
+        <v/>
+      </c>
+      <c r="O76">
+        <f>G76*I76</f>
+        <v/>
       </c>
       <c r="P76">
-        <f>G76*H76</f>
+        <f>G76*J76</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>G76*I76</f>
+        <f>G76*K76</f>
         <v/>
       </c>
       <c r="R76">
-        <f>G76*J76</f>
+        <f>G76*L76</f>
         <v/>
       </c>
       <c r="S76">
-        <f>G76*K76</f>
+        <f>G76*M76</f>
         <v/>
       </c>
       <c r="T76">
-        <f>G76*L76</f>
+        <f>SUM(N76:S76)</f>
         <v/>
       </c>
       <c r="U76">
-        <f>G76*M76</f>
+        <f>AVERAGE(H76:M76)</f>
         <v/>
       </c>
       <c r="V76">
-        <f>G76*N76</f>
-        <v/>
-      </c>
-      <c r="W76">
-        <f>G76*O76</f>
-        <v/>
-      </c>
-      <c r="X76">
-        <f>SUM(P76:W76)</f>
-        <v/>
-      </c>
-      <c r="Y76">
-        <f>AVERAGE(H76:O76)</f>
-        <v/>
-      </c>
-      <c r="Z76">
-        <f>X76-G76*8</f>
+        <f>T76-G76*6</f>
         <v/>
       </c>
     </row>
@@ -17813,7 +16511,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -17833,54 +16531,40 @@
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
+      <c r="N77">
+        <f>G77*H77</f>
+        <v/>
+      </c>
+      <c r="O77">
+        <f>G77*I77</f>
+        <v/>
       </c>
       <c r="P77">
-        <f>G77*H77</f>
+        <f>G77*J77</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>G77*I77</f>
+        <f>G77*K77</f>
         <v/>
       </c>
       <c r="R77">
-        <f>G77*J77</f>
+        <f>G77*L77</f>
         <v/>
       </c>
       <c r="S77">
-        <f>G77*K77</f>
+        <f>G77*M77</f>
         <v/>
       </c>
       <c r="T77">
-        <f>G77*L77</f>
+        <f>SUM(N77:S77)</f>
         <v/>
       </c>
       <c r="U77">
-        <f>G77*M77</f>
+        <f>AVERAGE(H77:M77)</f>
         <v/>
       </c>
       <c r="V77">
-        <f>G77*N77</f>
-        <v/>
-      </c>
-      <c r="W77">
-        <f>G77*O77</f>
-        <v/>
-      </c>
-      <c r="X77">
-        <f>SUM(P77:W77)</f>
-        <v/>
-      </c>
-      <c r="Y77">
-        <f>AVERAGE(H77:O77)</f>
-        <v/>
-      </c>
-      <c r="Z77">
-        <f>X77-G77*8</f>
+        <f>T77-G77*6</f>
         <v/>
       </c>
     </row>
@@ -17916,7 +16600,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -17936,54 +16620,40 @@
       <c r="M78" t="n">
         <v>0</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
+      <c r="N78">
+        <f>G78*H78</f>
+        <v/>
+      </c>
+      <c r="O78">
+        <f>G78*I78</f>
+        <v/>
       </c>
       <c r="P78">
-        <f>G78*H78</f>
+        <f>G78*J78</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>G78*I78</f>
+        <f>G78*K78</f>
         <v/>
       </c>
       <c r="R78">
-        <f>G78*J78</f>
+        <f>G78*L78</f>
         <v/>
       </c>
       <c r="S78">
-        <f>G78*K78</f>
+        <f>G78*M78</f>
         <v/>
       </c>
       <c r="T78">
-        <f>G78*L78</f>
+        <f>SUM(N78:S78)</f>
         <v/>
       </c>
       <c r="U78">
-        <f>G78*M78</f>
+        <f>AVERAGE(H78:M78)</f>
         <v/>
       </c>
       <c r="V78">
-        <f>G78*N78</f>
-        <v/>
-      </c>
-      <c r="W78">
-        <f>G78*O78</f>
-        <v/>
-      </c>
-      <c r="X78">
-        <f>SUM(P78:W78)</f>
-        <v/>
-      </c>
-      <c r="Y78">
-        <f>AVERAGE(H78:O78)</f>
-        <v/>
-      </c>
-      <c r="Z78">
-        <f>X78-G78*8</f>
+        <f>T78-G78*6</f>
         <v/>
       </c>
     </row>
@@ -18019,7 +16689,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -18039,54 +16709,40 @@
       <c r="M79" t="n">
         <v>0</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
+      <c r="N79">
+        <f>G79*H79</f>
+        <v/>
+      </c>
+      <c r="O79">
+        <f>G79*I79</f>
+        <v/>
       </c>
       <c r="P79">
-        <f>G79*H79</f>
+        <f>G79*J79</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>G79*I79</f>
+        <f>G79*K79</f>
         <v/>
       </c>
       <c r="R79">
-        <f>G79*J79</f>
+        <f>G79*L79</f>
         <v/>
       </c>
       <c r="S79">
-        <f>G79*K79</f>
+        <f>G79*M79</f>
         <v/>
       </c>
       <c r="T79">
-        <f>G79*L79</f>
+        <f>SUM(N79:S79)</f>
         <v/>
       </c>
       <c r="U79">
-        <f>G79*M79</f>
+        <f>AVERAGE(H79:M79)</f>
         <v/>
       </c>
       <c r="V79">
-        <f>G79*N79</f>
-        <v/>
-      </c>
-      <c r="W79">
-        <f>G79*O79</f>
-        <v/>
-      </c>
-      <c r="X79">
-        <f>SUM(P79:W79)</f>
-        <v/>
-      </c>
-      <c r="Y79">
-        <f>AVERAGE(H79:O79)</f>
-        <v/>
-      </c>
-      <c r="Z79">
-        <f>X79-G79*8</f>
+        <f>T79-G79*6</f>
         <v/>
       </c>
     </row>
@@ -18122,7 +16778,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -18142,54 +16798,40 @@
       <c r="M80" t="n">
         <v>0</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
+      <c r="N80">
+        <f>G80*H80</f>
+        <v/>
+      </c>
+      <c r="O80">
+        <f>G80*I80</f>
+        <v/>
       </c>
       <c r="P80">
-        <f>G80*H80</f>
+        <f>G80*J80</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>G80*I80</f>
+        <f>G80*K80</f>
         <v/>
       </c>
       <c r="R80">
-        <f>G80*J80</f>
+        <f>G80*L80</f>
         <v/>
       </c>
       <c r="S80">
-        <f>G80*K80</f>
+        <f>G80*M80</f>
         <v/>
       </c>
       <c r="T80">
-        <f>G80*L80</f>
+        <f>SUM(N80:S80)</f>
         <v/>
       </c>
       <c r="U80">
-        <f>G80*M80</f>
+        <f>AVERAGE(H80:M80)</f>
         <v/>
       </c>
       <c r="V80">
-        <f>G80*N80</f>
-        <v/>
-      </c>
-      <c r="W80">
-        <f>G80*O80</f>
-        <v/>
-      </c>
-      <c r="X80">
-        <f>SUM(P80:W80)</f>
-        <v/>
-      </c>
-      <c r="Y80">
-        <f>AVERAGE(H80:O80)</f>
-        <v/>
-      </c>
-      <c r="Z80">
-        <f>X80-G80*8</f>
+        <f>T80-G80*6</f>
         <v/>
       </c>
     </row>
@@ -18225,7 +16867,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -18245,54 +16887,40 @@
       <c r="M81" t="n">
         <v>0</v>
       </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
+      <c r="N81">
+        <f>G81*H81</f>
+        <v/>
+      </c>
+      <c r="O81">
+        <f>G81*I81</f>
+        <v/>
       </c>
       <c r="P81">
-        <f>G81*H81</f>
+        <f>G81*J81</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>G81*I81</f>
+        <f>G81*K81</f>
         <v/>
       </c>
       <c r="R81">
-        <f>G81*J81</f>
+        <f>G81*L81</f>
         <v/>
       </c>
       <c r="S81">
-        <f>G81*K81</f>
+        <f>G81*M81</f>
         <v/>
       </c>
       <c r="T81">
-        <f>G81*L81</f>
+        <f>SUM(N81:S81)</f>
         <v/>
       </c>
       <c r="U81">
-        <f>G81*M81</f>
+        <f>AVERAGE(H81:M81)</f>
         <v/>
       </c>
       <c r="V81">
-        <f>G81*N81</f>
-        <v/>
-      </c>
-      <c r="W81">
-        <f>G81*O81</f>
-        <v/>
-      </c>
-      <c r="X81">
-        <f>SUM(P81:W81)</f>
-        <v/>
-      </c>
-      <c r="Y81">
-        <f>AVERAGE(H81:O81)</f>
-        <v/>
-      </c>
-      <c r="Z81">
-        <f>X81-G81*8</f>
+        <f>T81-G81*6</f>
         <v/>
       </c>
     </row>
@@ -18328,7 +16956,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -18348,54 +16976,40 @@
       <c r="M82" t="n">
         <v>0</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
+      <c r="N82">
+        <f>G82*H82</f>
+        <v/>
+      </c>
+      <c r="O82">
+        <f>G82*I82</f>
+        <v/>
       </c>
       <c r="P82">
-        <f>G82*H82</f>
+        <f>G82*J82</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>G82*I82</f>
+        <f>G82*K82</f>
         <v/>
       </c>
       <c r="R82">
-        <f>G82*J82</f>
+        <f>G82*L82</f>
         <v/>
       </c>
       <c r="S82">
-        <f>G82*K82</f>
+        <f>G82*M82</f>
         <v/>
       </c>
       <c r="T82">
-        <f>G82*L82</f>
+        <f>SUM(N82:S82)</f>
         <v/>
       </c>
       <c r="U82">
-        <f>G82*M82</f>
+        <f>AVERAGE(H82:M82)</f>
         <v/>
       </c>
       <c r="V82">
-        <f>G82*N82</f>
-        <v/>
-      </c>
-      <c r="W82">
-        <f>G82*O82</f>
-        <v/>
-      </c>
-      <c r="X82">
-        <f>SUM(P82:W82)</f>
-        <v/>
-      </c>
-      <c r="Y82">
-        <f>AVERAGE(H82:O82)</f>
-        <v/>
-      </c>
-      <c r="Z82">
-        <f>X82-G82*8</f>
+        <f>T82-G82*6</f>
         <v/>
       </c>
     </row>
@@ -18431,7 +17045,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -18451,54 +17065,40 @@
       <c r="M83" t="n">
         <v>0</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
+      <c r="N83">
+        <f>G83*H83</f>
+        <v/>
+      </c>
+      <c r="O83">
+        <f>G83*I83</f>
+        <v/>
       </c>
       <c r="P83">
-        <f>G83*H83</f>
+        <f>G83*J83</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>G83*I83</f>
+        <f>G83*K83</f>
         <v/>
       </c>
       <c r="R83">
-        <f>G83*J83</f>
+        <f>G83*L83</f>
         <v/>
       </c>
       <c r="S83">
-        <f>G83*K83</f>
+        <f>G83*M83</f>
         <v/>
       </c>
       <c r="T83">
-        <f>G83*L83</f>
+        <f>SUM(N83:S83)</f>
         <v/>
       </c>
       <c r="U83">
-        <f>G83*M83</f>
+        <f>AVERAGE(H83:M83)</f>
         <v/>
       </c>
       <c r="V83">
-        <f>G83*N83</f>
-        <v/>
-      </c>
-      <c r="W83">
-        <f>G83*O83</f>
-        <v/>
-      </c>
-      <c r="X83">
-        <f>SUM(P83:W83)</f>
-        <v/>
-      </c>
-      <c r="Y83">
-        <f>AVERAGE(H83:O83)</f>
-        <v/>
-      </c>
-      <c r="Z83">
-        <f>X83-G83*8</f>
+        <f>T83-G83*6</f>
         <v/>
       </c>
     </row>
@@ -18534,7 +17134,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -18554,54 +17154,40 @@
       <c r="M84" t="n">
         <v>0</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
+      <c r="N84">
+        <f>G84*H84</f>
+        <v/>
+      </c>
+      <c r="O84">
+        <f>G84*I84</f>
+        <v/>
       </c>
       <c r="P84">
-        <f>G84*H84</f>
+        <f>G84*J84</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>G84*I84</f>
+        <f>G84*K84</f>
         <v/>
       </c>
       <c r="R84">
-        <f>G84*J84</f>
+        <f>G84*L84</f>
         <v/>
       </c>
       <c r="S84">
-        <f>G84*K84</f>
+        <f>G84*M84</f>
         <v/>
       </c>
       <c r="T84">
-        <f>G84*L84</f>
+        <f>SUM(N84:S84)</f>
         <v/>
       </c>
       <c r="U84">
-        <f>G84*M84</f>
+        <f>AVERAGE(H84:M84)</f>
         <v/>
       </c>
       <c r="V84">
-        <f>G84*N84</f>
-        <v/>
-      </c>
-      <c r="W84">
-        <f>G84*O84</f>
-        <v/>
-      </c>
-      <c r="X84">
-        <f>SUM(P84:W84)</f>
-        <v/>
-      </c>
-      <c r="Y84">
-        <f>AVERAGE(H84:O84)</f>
-        <v/>
-      </c>
-      <c r="Z84">
-        <f>X84-G84*8</f>
+        <f>T84-G84*6</f>
         <v/>
       </c>
     </row>
@@ -18637,7 +17223,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -18657,54 +17243,40 @@
       <c r="M85" t="n">
         <v>0</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
+      <c r="N85">
+        <f>G85*H85</f>
+        <v/>
+      </c>
+      <c r="O85">
+        <f>G85*I85</f>
+        <v/>
       </c>
       <c r="P85">
-        <f>G85*H85</f>
+        <f>G85*J85</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>G85*I85</f>
+        <f>G85*K85</f>
         <v/>
       </c>
       <c r="R85">
-        <f>G85*J85</f>
+        <f>G85*L85</f>
         <v/>
       </c>
       <c r="S85">
-        <f>G85*K85</f>
+        <f>G85*M85</f>
         <v/>
       </c>
       <c r="T85">
-        <f>G85*L85</f>
+        <f>SUM(N85:S85)</f>
         <v/>
       </c>
       <c r="U85">
-        <f>G85*M85</f>
+        <f>AVERAGE(H85:M85)</f>
         <v/>
       </c>
       <c r="V85">
-        <f>G85*N85</f>
-        <v/>
-      </c>
-      <c r="W85">
-        <f>G85*O85</f>
-        <v/>
-      </c>
-      <c r="X85">
-        <f>SUM(P85:W85)</f>
-        <v/>
-      </c>
-      <c r="Y85">
-        <f>AVERAGE(H85:O85)</f>
-        <v/>
-      </c>
-      <c r="Z85">
-        <f>X85-G85*8</f>
+        <f>T85-G85*6</f>
         <v/>
       </c>
     </row>
@@ -18740,7 +17312,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -18760,54 +17332,40 @@
       <c r="M86" t="n">
         <v>0</v>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
+      <c r="N86">
+        <f>G86*H86</f>
+        <v/>
+      </c>
+      <c r="O86">
+        <f>G86*I86</f>
+        <v/>
       </c>
       <c r="P86">
-        <f>G86*H86</f>
+        <f>G86*J86</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>G86*I86</f>
+        <f>G86*K86</f>
         <v/>
       </c>
       <c r="R86">
-        <f>G86*J86</f>
+        <f>G86*L86</f>
         <v/>
       </c>
       <c r="S86">
-        <f>G86*K86</f>
+        <f>G86*M86</f>
         <v/>
       </c>
       <c r="T86">
-        <f>G86*L86</f>
+        <f>SUM(N86:S86)</f>
         <v/>
       </c>
       <c r="U86">
-        <f>G86*M86</f>
+        <f>AVERAGE(H86:M86)</f>
         <v/>
       </c>
       <c r="V86">
-        <f>G86*N86</f>
-        <v/>
-      </c>
-      <c r="W86">
-        <f>G86*O86</f>
-        <v/>
-      </c>
-      <c r="X86">
-        <f>SUM(P86:W86)</f>
-        <v/>
-      </c>
-      <c r="Y86">
-        <f>AVERAGE(H86:O86)</f>
-        <v/>
-      </c>
-      <c r="Z86">
-        <f>X86-G86*8</f>
+        <f>T86-G86*6</f>
         <v/>
       </c>
     </row>
@@ -18843,7 +17401,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -18863,54 +17421,40 @@
       <c r="M87" t="n">
         <v>0</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
+      <c r="N87">
+        <f>G87*H87</f>
+        <v/>
+      </c>
+      <c r="O87">
+        <f>G87*I87</f>
+        <v/>
       </c>
       <c r="P87">
-        <f>G87*H87</f>
+        <f>G87*J87</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>G87*I87</f>
+        <f>G87*K87</f>
         <v/>
       </c>
       <c r="R87">
-        <f>G87*J87</f>
+        <f>G87*L87</f>
         <v/>
       </c>
       <c r="S87">
-        <f>G87*K87</f>
+        <f>G87*M87</f>
         <v/>
       </c>
       <c r="T87">
-        <f>G87*L87</f>
+        <f>SUM(N87:S87)</f>
         <v/>
       </c>
       <c r="U87">
-        <f>G87*M87</f>
+        <f>AVERAGE(H87:M87)</f>
         <v/>
       </c>
       <c r="V87">
-        <f>G87*N87</f>
-        <v/>
-      </c>
-      <c r="W87">
-        <f>G87*O87</f>
-        <v/>
-      </c>
-      <c r="X87">
-        <f>SUM(P87:W87)</f>
-        <v/>
-      </c>
-      <c r="Y87">
-        <f>AVERAGE(H87:O87)</f>
-        <v/>
-      </c>
-      <c r="Z87">
-        <f>X87-G87*8</f>
+        <f>T87-G87*6</f>
         <v/>
       </c>
     </row>
@@ -18946,7 +17490,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -18966,54 +17510,40 @@
       <c r="M88" t="n">
         <v>0</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
+      <c r="N88">
+        <f>G88*H88</f>
+        <v/>
+      </c>
+      <c r="O88">
+        <f>G88*I88</f>
+        <v/>
       </c>
       <c r="P88">
-        <f>G88*H88</f>
+        <f>G88*J88</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>G88*I88</f>
+        <f>G88*K88</f>
         <v/>
       </c>
       <c r="R88">
-        <f>G88*J88</f>
+        <f>G88*L88</f>
         <v/>
       </c>
       <c r="S88">
-        <f>G88*K88</f>
+        <f>G88*M88</f>
         <v/>
       </c>
       <c r="T88">
-        <f>G88*L88</f>
+        <f>SUM(N88:S88)</f>
         <v/>
       </c>
       <c r="U88">
-        <f>G88*M88</f>
+        <f>AVERAGE(H88:M88)</f>
         <v/>
       </c>
       <c r="V88">
-        <f>G88*N88</f>
-        <v/>
-      </c>
-      <c r="W88">
-        <f>G88*O88</f>
-        <v/>
-      </c>
-      <c r="X88">
-        <f>SUM(P88:W88)</f>
-        <v/>
-      </c>
-      <c r="Y88">
-        <f>AVERAGE(H88:O88)</f>
-        <v/>
-      </c>
-      <c r="Z88">
-        <f>X88-G88*8</f>
+        <f>T88-G88*6</f>
         <v/>
       </c>
     </row>
@@ -19049,7 +17579,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -19069,54 +17599,40 @@
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
+      <c r="N89">
+        <f>G89*H89</f>
+        <v/>
+      </c>
+      <c r="O89">
+        <f>G89*I89</f>
+        <v/>
       </c>
       <c r="P89">
-        <f>G89*H89</f>
+        <f>G89*J89</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>G89*I89</f>
+        <f>G89*K89</f>
         <v/>
       </c>
       <c r="R89">
-        <f>G89*J89</f>
+        <f>G89*L89</f>
         <v/>
       </c>
       <c r="S89">
-        <f>G89*K89</f>
+        <f>G89*M89</f>
         <v/>
       </c>
       <c r="T89">
-        <f>G89*L89</f>
+        <f>SUM(N89:S89)</f>
         <v/>
       </c>
       <c r="U89">
-        <f>G89*M89</f>
+        <f>AVERAGE(H89:M89)</f>
         <v/>
       </c>
       <c r="V89">
-        <f>G89*N89</f>
-        <v/>
-      </c>
-      <c r="W89">
-        <f>G89*O89</f>
-        <v/>
-      </c>
-      <c r="X89">
-        <f>SUM(P89:W89)</f>
-        <v/>
-      </c>
-      <c r="Y89">
-        <f>AVERAGE(H89:O89)</f>
-        <v/>
-      </c>
-      <c r="Z89">
-        <f>X89-G89*8</f>
+        <f>T89-G89*6</f>
         <v/>
       </c>
     </row>
@@ -19152,7 +17668,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -19172,54 +17688,40 @@
       <c r="M90" t="n">
         <v>0</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
+      <c r="N90">
+        <f>G90*H90</f>
+        <v/>
+      </c>
+      <c r="O90">
+        <f>G90*I90</f>
+        <v/>
       </c>
       <c r="P90">
-        <f>G90*H90</f>
+        <f>G90*J90</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>G90*I90</f>
+        <f>G90*K90</f>
         <v/>
       </c>
       <c r="R90">
-        <f>G90*J90</f>
+        <f>G90*L90</f>
         <v/>
       </c>
       <c r="S90">
-        <f>G90*K90</f>
+        <f>G90*M90</f>
         <v/>
       </c>
       <c r="T90">
-        <f>G90*L90</f>
+        <f>SUM(N90:S90)</f>
         <v/>
       </c>
       <c r="U90">
-        <f>G90*M90</f>
+        <f>AVERAGE(H90:M90)</f>
         <v/>
       </c>
       <c r="V90">
-        <f>G90*N90</f>
-        <v/>
-      </c>
-      <c r="W90">
-        <f>G90*O90</f>
-        <v/>
-      </c>
-      <c r="X90">
-        <f>SUM(P90:W90)</f>
-        <v/>
-      </c>
-      <c r="Y90">
-        <f>AVERAGE(H90:O90)</f>
-        <v/>
-      </c>
-      <c r="Z90">
-        <f>X90-G90*8</f>
+        <f>T90-G90*6</f>
         <v/>
       </c>
     </row>
@@ -19255,7 +17757,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -19275,54 +17777,40 @@
       <c r="M91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
+      <c r="N91">
+        <f>G91*H91</f>
+        <v/>
+      </c>
+      <c r="O91">
+        <f>G91*I91</f>
+        <v/>
       </c>
       <c r="P91">
-        <f>G91*H91</f>
+        <f>G91*J91</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>G91*I91</f>
+        <f>G91*K91</f>
         <v/>
       </c>
       <c r="R91">
-        <f>G91*J91</f>
+        <f>G91*L91</f>
         <v/>
       </c>
       <c r="S91">
-        <f>G91*K91</f>
+        <f>G91*M91</f>
         <v/>
       </c>
       <c r="T91">
-        <f>G91*L91</f>
+        <f>SUM(N91:S91)</f>
         <v/>
       </c>
       <c r="U91">
-        <f>G91*M91</f>
+        <f>AVERAGE(H91:M91)</f>
         <v/>
       </c>
       <c r="V91">
-        <f>G91*N91</f>
-        <v/>
-      </c>
-      <c r="W91">
-        <f>G91*O91</f>
-        <v/>
-      </c>
-      <c r="X91">
-        <f>SUM(P91:W91)</f>
-        <v/>
-      </c>
-      <c r="Y91">
-        <f>AVERAGE(H91:O91)</f>
-        <v/>
-      </c>
-      <c r="Z91">
-        <f>X91-G91*8</f>
+        <f>T91-G91*6</f>
         <v/>
       </c>
     </row>
@@ -19358,7 +17846,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -19378,54 +17866,40 @@
       <c r="M92" t="n">
         <v>0</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
+      <c r="N92">
+        <f>G92*H92</f>
+        <v/>
+      </c>
+      <c r="O92">
+        <f>G92*I92</f>
+        <v/>
       </c>
       <c r="P92">
-        <f>G92*H92</f>
+        <f>G92*J92</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>G92*I92</f>
+        <f>G92*K92</f>
         <v/>
       </c>
       <c r="R92">
-        <f>G92*J92</f>
+        <f>G92*L92</f>
         <v/>
       </c>
       <c r="S92">
-        <f>G92*K92</f>
+        <f>G92*M92</f>
         <v/>
       </c>
       <c r="T92">
-        <f>G92*L92</f>
+        <f>SUM(N92:S92)</f>
         <v/>
       </c>
       <c r="U92">
-        <f>G92*M92</f>
+        <f>AVERAGE(H92:M92)</f>
         <v/>
       </c>
       <c r="V92">
-        <f>G92*N92</f>
-        <v/>
-      </c>
-      <c r="W92">
-        <f>G92*O92</f>
-        <v/>
-      </c>
-      <c r="X92">
-        <f>SUM(P92:W92)</f>
-        <v/>
-      </c>
-      <c r="Y92">
-        <f>AVERAGE(H92:O92)</f>
-        <v/>
-      </c>
-      <c r="Z92">
-        <f>X92-G92*8</f>
+        <f>T92-G92*6</f>
         <v/>
       </c>
     </row>

--- a/ACME_Project_Team_Workload.xlsx
+++ b/ACME_Project_Team_Workload.xlsx
@@ -2375,8 +2375,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2419,8 +2417,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2463,8 +2459,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2507,8 +2501,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2551,8 +2543,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2595,8 +2585,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2639,8 +2627,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2683,8 +2669,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2727,8 +2711,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2771,8 +2753,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2815,8 +2795,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2859,8 +2837,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2903,8 +2879,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2947,8 +2921,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2991,8 +2963,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3035,8 +3005,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3079,8 +3047,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3123,8 +3089,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3167,8 +3131,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3211,8 +3173,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3255,8 +3215,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3299,8 +3257,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3343,8 +3299,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3387,8 +3341,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3431,8 +3383,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3475,8 +3425,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3519,8 +3467,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3563,8 +3509,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3607,8 +3551,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3651,8 +3593,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3695,8 +3635,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3739,8 +3677,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3783,8 +3719,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3827,8 +3761,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3871,8 +3803,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3976,7 +3906,6 @@
           <t>Batman</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4014,7 +3943,6 @@
           <t>Superman</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4052,7 +3980,6 @@
           <t>Wonder Woman</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4090,7 +4017,6 @@
           <t>Iron Man</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4128,7 +4054,6 @@
           <t>Captain America</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4166,7 +4091,6 @@
           <t>Professor X</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4204,7 +4128,6 @@
           <t>Cyclops</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4242,7 +4165,6 @@
           <t>Storm</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4280,7 +4202,6 @@
           <t>Reed Richards</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4318,7 +4239,6 @@
           <t>Sue Storm</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4356,7 +4276,6 @@
           <t>Raven</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4394,7 +4313,6 @@
           <t>Robin</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4432,7 +4350,6 @@
           <t>Cyborg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4470,7 +4387,6 @@
           <t>Star-Lord</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4508,7 +4424,6 @@
           <t>Rocket</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4546,7 +4461,6 @@
           <t>Nick Fury</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4584,7 +4498,6 @@
           <t>Black Widow</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4622,7 +4535,6 @@
           <t>Doctor Strange</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4660,7 +4572,6 @@
           <t>Rorschach</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4698,7 +4609,6 @@
           <t>Ozymandias</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4736,7 +4646,6 @@
           <t>Vision</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4774,7 +4683,6 @@
           <t>Hawkeye</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4812,7 +4720,6 @@
           <t>Scarlet Witch</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4850,7 +4757,6 @@
           <t>Martian Manhunter</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4888,7 +4794,6 @@
           <t>Green Lantern</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4926,7 +4831,6 @@
           <t>Jean Grey</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4964,7 +4868,6 @@
           <t>Wolverine</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5002,7 +4905,6 @@
           <t>Magneto</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5040,7 +4942,6 @@
           <t>Reed Richards</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5078,7 +4979,6 @@
           <t>Thing</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5116,7 +5016,6 @@
           <t>Thor</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5154,7 +5053,6 @@
           <t>Hulk</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5192,7 +5090,6 @@
           <t>Ant-Man</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5230,7 +5127,6 @@
           <t>Flash</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5268,7 +5164,6 @@
           <t>Aquaman</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5306,7 +5201,6 @@
           <t>Clint Barton</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5344,7 +5238,6 @@
           <t>Dane Whitman</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5382,7 +5275,6 @@
           <t>Nebula</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5420,7 +5312,6 @@
           <t>Yelena Belova</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5458,7 +5349,6 @@
           <t>Kate Bishop</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5496,7 +5386,6 @@
           <t>Peter Parker</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5534,7 +5423,6 @@
           <t>Luke Cage</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5572,7 +5460,6 @@
           <t>Sam Wilson</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5610,7 +5497,6 @@
           <t>Gamora</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5648,7 +5534,6 @@
           <t>Monica Rambeau</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5686,7 +5571,6 @@
           <t>Ben Grimm</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5724,7 +5608,6 @@
           <t>Maria Hill</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5762,7 +5645,6 @@
           <t>Matt Murdock</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5800,7 +5682,6 @@
           <t>Stephen Strange</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5838,7 +5719,6 @@
           <t>Pepper Potts</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5876,7 +5756,6 @@
           <t>Carol Danvers</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5914,7 +5793,6 @@
           <t>Jessica Jones</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5952,7 +5830,6 @@
           <t>Quake Johnson</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5990,7 +5867,6 @@
           <t>Bucky Barnes</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6028,7 +5904,6 @@
           <t>Tony Stark</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6066,7 +5941,6 @@
           <t>Frank Castle</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6104,7 +5978,6 @@
           <t>T'Challa</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6142,7 +6015,6 @@
           <t>Steve Rogers</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6180,7 +6052,6 @@
           <t>Shang-Chi</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6218,7 +6089,6 @@
           <t>Rene Ramirez</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6256,7 +6126,6 @@
           <t>Tim Drake</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6294,7 +6163,6 @@
           <t>Helena Bertinelli</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6332,7 +6200,6 @@
           <t>Dinah Lance</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6370,7 +6237,6 @@
           <t>Stephanie Brown</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6408,7 +6274,6 @@
           <t>Kendra Saunders</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6446,7 +6311,6 @@
           <t>Mari McCabe</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6484,7 +6348,6 @@
           <t>Victor Zsasz</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6522,7 +6385,6 @@
           <t>Carter Hall</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6560,7 +6422,6 @@
           <t>John Stewart</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6598,7 +6459,6 @@
           <t>Zatanna Zatara</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6636,7 +6496,6 @@
           <t>Kaldur'ahm</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6674,7 +6533,6 @@
           <t>Ryan Choi</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6712,7 +6570,6 @@
           <t>Donna Troy</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6750,7 +6607,6 @@
           <t>Eobard Thawne</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6788,7 +6644,6 @@
           <t>Barbara Gordon</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6826,7 +6681,6 @@
           <t>Shuri</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6864,7 +6718,6 @@
           <t>Danny Rand</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6902,7 +6755,6 @@
           <t>Johnny Storm</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6940,7 +6792,6 @@
           <t>Bruce Banner</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6978,7 +6829,6 @@
           <t>Groot</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7016,7 +6866,6 @@
           <t>Okoye</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7054,7 +6903,6 @@
           <t>Hank Pym</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7092,7 +6940,6 @@
           <t>Jennifer Walters</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7130,7 +6977,6 @@
           <t>Rory Regan</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7168,7 +7014,6 @@
           <t>Huntress Wayne</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7206,7 +7051,6 @@
           <t>Oliver Queen</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7244,7 +7088,6 @@
           <t>Ravager Wilson</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7282,7 +7125,6 @@
           <t>Cassandra Cain</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7320,7 +7162,6 @@
           <t>Kara Zor-El</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7358,7 +7199,6 @@
           <t>Wally West</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7396,7 +7236,6 @@
           <t>Talia al Ghul</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9836,7 +9675,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -9925,7 +9764,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -10014,7 +9853,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -10103,7 +9942,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -10192,7 +10031,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -10281,7 +10120,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -10370,7 +10209,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10459,7 +10298,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10548,7 +10387,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10637,7 +10476,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10726,7 +10565,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10815,7 +10654,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10904,7 +10743,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10993,7 +10832,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -11082,7 +10921,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -11171,7 +11010,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -11260,7 +11099,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -11349,7 +11188,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -11438,7 +11277,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -11527,7 +11366,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -11616,7 +11455,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -11705,7 +11544,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -11794,7 +11633,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -11883,7 +11722,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -11972,7 +11811,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -12061,7 +11900,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -12150,7 +11989,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -12239,7 +12078,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -12328,7 +12167,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -12417,7 +12256,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -12506,7 +12345,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -12595,7 +12434,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -12684,7 +12523,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -12773,7 +12612,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -12862,7 +12701,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -12951,7 +12790,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -13040,7 +12879,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -13129,7 +12968,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -13218,7 +13057,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -13307,7 +13146,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -13396,7 +13235,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -13485,7 +13324,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -13574,7 +13413,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -13663,7 +13502,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -13752,7 +13591,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -13841,7 +13680,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -13930,7 +13769,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -14019,7 +13858,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -14108,7 +13947,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -14197,7 +14036,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -14286,7 +14125,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -14375,7 +14214,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -14464,7 +14303,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -14553,7 +14392,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -14642,7 +14481,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -14731,7 +14570,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -14820,7 +14659,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -14909,7 +14748,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -14998,7 +14837,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -15087,7 +14926,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -15176,7 +15015,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -15265,7 +15104,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -15354,7 +15193,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -15443,7 +15282,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -15532,7 +15371,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -15621,7 +15460,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -15710,7 +15549,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -15799,7 +15638,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -15888,7 +15727,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -15977,7 +15816,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -16066,7 +15905,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -16155,7 +15994,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -16244,7 +16083,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -16333,7 +16172,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -16422,7 +16261,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -16511,7 +16350,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -16600,7 +16439,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -16689,7 +16528,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -16778,7 +16617,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -16867,7 +16706,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -16956,7 +16795,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -17045,7 +16884,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -17134,7 +16973,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -17223,7 +17062,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -17312,7 +17151,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -17401,7 +17240,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -17490,7 +17329,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -17579,7 +17418,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -17668,7 +17507,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -17757,7 +17596,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -17846,7 +17685,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
